--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>1304</v>
       </c>
       <c r="M6" s="1">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>1301</v>
       </c>
       <c r="M8" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>1304</v>
       </c>
       <c r="M6" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>1301</v>
       </c>
       <c r="M8" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="N8" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1806,7 +1806,7 @@
         <v>1399</v>
       </c>
       <c r="M7" s="1">
-        <v>999999</v>
+        <v>5000</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1229,7 +1229,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1490,7 +1490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" ht="28.8" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>1304</v>
       </c>
       <c r="M6" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
@@ -1806,7 +1806,7 @@
         <v>1399</v>
       </c>
       <c r="M7" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>1301</v>
       </c>
       <c r="M8" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="N8" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1229,7 +1229,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1490,7 +1490,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:32">
+    <row r="4" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>1304</v>
       </c>
       <c r="M6" s="1">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
@@ -1806,7 +1806,7 @@
         <v>1399</v>
       </c>
       <c r="M7" s="1">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>1301</v>
       </c>
       <c r="M8" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N8" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1622,7 +1622,7 @@
         <v>1301</v>
       </c>
       <c r="M5" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N5" s="1">
         <v>100</v>
@@ -1716,7 +1716,7 @@
         <v>1304</v>
       </c>
       <c r="M6" s="1">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="N6" s="1">
         <v>100</v>
@@ -1806,7 +1806,7 @@
         <v>1399</v>
       </c>
       <c r="M7" s="1">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>1301</v>
       </c>
       <c r="M8" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="N8" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1625,10 +1625,10 @@
         <v>400</v>
       </c>
       <c r="N5" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O5" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="P5" s="1">
         <v>10</v>
@@ -1719,10 +1719,10 @@
         <v>300</v>
       </c>
       <c r="N6" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O6" s="1">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
@@ -1809,7 +1809,7 @@
         <v>9999</v>
       </c>
       <c r="N7" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>400</v>
       </c>
       <c r="N8" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="O8" s="1">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1625,10 +1625,10 @@
         <v>400</v>
       </c>
       <c r="N5" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O5" s="1">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="P5" s="1">
         <v>10</v>
@@ -1809,7 +1809,7 @@
         <v>9999</v>
       </c>
       <c r="N7" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>400</v>
       </c>
       <c r="N8" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O8" s="1">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1958,7 +1958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" ht="12" customHeight="1" spans="1:32">
       <c r="B9">
         <v>1001</v>
       </c>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1722,7 +1722,7 @@
         <v>1000</v>
       </c>
       <c r="O6" s="1">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -1806,7 +1806,7 @@
         <v>1399</v>
       </c>
       <c r="M7" s="1">
-        <v>9999</v>
+        <v>2000</v>
       </c>
       <c r="N7" s="1">
         <v>100</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="118">
   <si>
     <t>#</t>
   </si>
@@ -35,7 +35,7 @@
     <t>SummonChessTable</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>Id</t>
   </si>
   <si>
     <t>Name</t>
@@ -53,12 +53,6 @@
     <t>Classes</t>
   </si>
   <si>
-    <t>StarLevel</t>
-  </si>
-  <si>
-    <t>NextStarId</t>
-  </si>
-  <si>
     <t>PrefabId</t>
   </si>
   <si>
@@ -134,9 +128,15 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>double[]</t>
+  </si>
+  <si>
     <t>double</t>
   </si>
   <si>
+    <t>string[]</t>
+  </si>
+  <si>
     <t>棋子的唯一配置ID</t>
   </si>
   <si>
@@ -158,76 +158,70 @@
     <t>职业ID数组（用于触发羁绊，如：3）</t>
   </si>
   <si>
-    <t>星级（1, 2, 3）</t>
-  </si>
-  <si>
-    <t>进化到下一星级的配置ID（3星填0）</t>
-  </si>
-  <si>
-    <t>棋子预制体资源ID</t>
-  </si>
-  <si>
-    <t>UI图标资源ID</t>
-  </si>
-  <si>
-    <t>最大生命值</t>
-  </si>
-  <si>
-    <t>最大法力值</t>
-  </si>
-  <si>
-    <t>初始法力值</t>
-  </si>
-  <si>
-    <t>攻击力（物理伤害）</t>
-  </si>
-  <si>
-    <t>攻击速度（每秒攻击次数）</t>
-  </si>
-  <si>
-    <t>攻击距离（格子数或米）</t>
-  </si>
-  <si>
-    <t>护甲（物理减伤）</t>
-  </si>
-  <si>
-    <t>魔抗（魔法减伤）</t>
+    <t>棋子预制体资源ID（阶级数组，暂时三阶相同）</t>
+  </si>
+  <si>
+    <t>UI图标资源ID（阶级数组，暂时三阶相同）</t>
+  </si>
+  <si>
+    <t>最大生命值（三个阶级）</t>
+  </si>
+  <si>
+    <t>最大法力值（三个阶级）</t>
+  </si>
+  <si>
+    <t>初始法力值（三个阶级）</t>
+  </si>
+  <si>
+    <t>攻击力（三个阶级）</t>
+  </si>
+  <si>
+    <t>攻击速度（三个阶级）</t>
+  </si>
+  <si>
+    <t>攻击距离（三个阶级）</t>
+  </si>
+  <si>
+    <t>护甲（三个阶级）</t>
+  </si>
+  <si>
+    <t>魔抗（三个阶级）</t>
   </si>
   <si>
     <t>移动速度</t>
   </si>
   <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>暴击伤害倍率</t>
-  </si>
-  <si>
-    <t>法术强度</t>
+    <t>暴击率（三个阶级）</t>
+  </si>
+  <si>
+    <t>暴击伤害倍率（三个阶级）</t>
+  </si>
+  <si>
+    <t>法术强度（三个阶级）</t>
   </si>
   <si>
     <t>护盾值</t>
   </si>
   <si>
-    <t>冷却缩减（百分比）</t>
-  </si>
-  <si>
-    <t>被动技能ID数组</t>
-  </si>
-  <si>
-    <t>普攻效果技能ID</t>
-  </si>
-  <si>
-    <t>技能一ID</t>
-  </si>
-  <si>
-    <t>大招ID</t>
+    <t>冷却缩减</t>
+  </si>
+  <si>
+    <t>被动技能ID数组（三个值，暂时相同）</t>
+  </si>
+  <si>
+    <t>普攻效果技能ID（三个值，暂时相同）</t>
+  </si>
+  <si>
+    <t>技能一ID（三个值，暂时相同）</t>
+  </si>
+  <si>
+    <t>大招ID（三个值，暂时相同）</t>
   </si>
   <si>
     <t>棋子AI模式:1=近战寻敌2=远程站桩3=稻草人</t>
   </si>
   <si>
-    <t>棋子的背景描述</t>
+    <t>棋子的背景描述（三个值：一阶/二阶/三阶）</t>
   </si>
   <si>
     <t>后羿</t>
@@ -236,10 +230,55 @@
     <t>1</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>暂无</t>
+    <t>2301,2301,2301</t>
+  </si>
+  <si>
+    <t>1301,1301,1301</t>
+  </si>
+  <si>
+    <t>400,580,800</t>
+  </si>
+  <si>
+    <t>100,100,100</t>
+  </si>
+  <si>
+    <t>60,60,60</t>
+  </si>
+  <si>
+    <t>10,16,26</t>
+  </si>
+  <si>
+    <t>0.5,0.65,0.8</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>20,25,30</t>
+  </si>
+  <si>
+    <t>0.15,0.2,0.25</t>
+  </si>
+  <si>
+    <t>1.5,1.7,2.0</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>11,11,11</t>
+  </si>
+  <si>
+    <t>12,12,12</t>
+  </si>
+  <si>
+    <t>13,13,13</t>
+  </si>
+  <si>
+    <t>14,14,14</t>
+  </si>
+  <si>
+    <t>暂无,暂无,暂无</t>
   </si>
   <si>
     <t>嫦娥</t>
@@ -248,19 +287,100 @@
     <t>3</t>
   </si>
   <si>
-    <t>21</t>
+    <t>2304,2304,2304</t>
+  </si>
+  <si>
+    <t>1304,1304,1304</t>
+  </si>
+  <si>
+    <t>300,420,580</t>
+  </si>
+  <si>
+    <t>1000,1000,1000</t>
+  </si>
+  <si>
+    <t>80,80,80</t>
+  </si>
+  <si>
+    <t>5,7,10</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>10,12,15</t>
+  </si>
+  <si>
+    <t>25,35,45</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>15,28,45</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>敌人测试</t>
+  </si>
+  <si>
+    <t>2309,2309,2309</t>
+  </si>
+  <si>
+    <t>400,400,400</t>
+  </si>
+  <si>
+    <t>10,10,10</t>
+  </si>
+  <si>
+    <t>0.5,0.5,0.5</t>
+  </si>
+  <si>
+    <t>20,20,20</t>
   </si>
   <si>
     <t>稻草人</t>
   </si>
   <si>
-    <t>测试用稻草人</t>
-  </si>
-  <si>
-    <t>敌人测试</t>
+    <t>2399,2399,2399</t>
+  </si>
+  <si>
+    <t>1399,1399,1399</t>
+  </si>
+  <si>
+    <t>2000,2000,2000</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>召唤师-狂战士</t>
+  </si>
+  <si>
+    <t>2101,2101,2101</t>
+  </si>
+  <si>
+    <t>1105,1105,1105</t>
+  </si>
+  <si>
+    <t>6,6,6</t>
   </si>
 </sst>
 </file>
@@ -1228,39 +1348,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="26" customWidth="1"/>
-    <col min="18" max="18" width="24" customWidth="1"/>
-    <col min="19" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="10" customWidth="1"/>
-    <col min="23" max="23" width="14" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="28" width="16" customWidth="1"/>
-    <col min="29" max="30" width="10" customWidth="1"/>
-    <col min="31" max="31" width="41" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="9" max="9" width="44" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="16" width="22" customWidth="1"/>
+    <col min="17" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
+    <col min="21" max="21" width="26" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="8" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="26" width="36" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
+    <col min="28" max="28" width="28" customWidth="1"/>
+    <col min="29" max="29" width="41" customWidth="1"/>
+    <col min="30" max="30" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,32 +1391,30 @@
       <c r="F1" s="1"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
       <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
-      <c r="AB1" s="1"/>
+      <c r="AB1" s="2"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
+      <c r="AD1" s="2"/>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:30">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1321,46 +1437,46 @@
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>21</v>
       </c>
       <c r="W2" s="1" t="s">
@@ -1369,128 +1485,116 @@
       <c r="X2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AA2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:30">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="L3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="Z3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="AA3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="AB3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:30">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1515,46 +1619,46 @@
       <c r="H4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="O4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" s="2" t="s">
         <v>52</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="V4" s="2" t="s">
         <v>56</v>
       </c>
       <c r="W4" s="1" t="s">
@@ -1563,39 +1667,33 @@
       <c r="X4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="Z4" s="2" t="s">
         <v>60</v>
       </c>
       <c r="AA4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AD4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:32">
+    <row r="5" ht="15" customHeight="1" spans="1:30">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -1604,92 +1702,86 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2301</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1301</v>
-      </c>
-      <c r="M5" s="1">
-        <v>400</v>
-      </c>
-      <c r="N5" s="1">
-        <v>100</v>
-      </c>
-      <c r="O5" s="1">
-        <v>60</v>
-      </c>
-      <c r="P5" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="R5" s="1">
-        <v>10</v>
+      <c r="K5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="S5" s="1">
-        <v>20</v>
-      </c>
-      <c r="T5" s="1">
-        <v>20</v>
-      </c>
-      <c r="U5" s="1">
         <v>3</v>
       </c>
-      <c r="V5" s="1">
-        <v>0.15</v>
+      <c r="T5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="W5" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
       </c>
-      <c r="Y5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>0</v>
+      <c r="Y5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>12</v>
+        <v>81</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="AC5" s="1">
-        <v>13</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>14</v>
-      </c>
-      <c r="AE5" s="1">
         <v>2</v>
       </c>
-      <c r="AF5" s="1" t="s">
-        <v>70</v>
+      <c r="AD5" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:32">
+    <row r="6" ht="15" customHeight="1" spans="1:30">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1698,347 +1790,328 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-      <c r="J6" s="1">
-        <v>5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2304</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1304</v>
-      </c>
-      <c r="M6" s="1">
-        <v>300</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="O6" s="1">
-        <v>80</v>
-      </c>
-      <c r="P6" s="1">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1">
-        <v>8</v>
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="S6" s="1">
-        <v>10</v>
-      </c>
-      <c r="T6" s="1">
-        <v>25</v>
-      </c>
-      <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="V6" s="1">
-        <v>0.15</v>
+      <c r="T6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="W6" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>15</v>
-      </c>
-      <c r="Y6" s="1">
         <v>0</v>
       </c>
-      <c r="Z6" s="1">
-        <v>0</v>
+      <c r="Y6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>22</v>
+        <v>101</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="AC6" s="1">
-        <v>23</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>24</v>
-      </c>
-      <c r="AE6" s="1">
         <v>2</v>
       </c>
-      <c r="AF6" s="1" t="s">
-        <v>70</v>
+      <c r="AD6" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:32">
+    <row r="7" ht="15" customHeight="1" spans="1:30">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
-        <v>9999</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S7" s="1">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W7" s="1">
         <v>0</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>2399</v>
-      </c>
-      <c r="L7" s="1">
-        <v>1399</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2000</v>
-      </c>
-      <c r="N7" s="1">
-        <v>100</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1</v>
-      </c>
-      <c r="R7" s="1">
-        <v>1</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
-      </c>
-      <c r="W7" s="1">
-        <v>1.5</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
       </c>
-      <c r="Y7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="1">
-        <v>0</v>
+      <c r="Y7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="AC7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>75</v>
+        <v>2</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:32">
+    <row r="8" ht="15" customHeight="1" spans="1:30">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
-        <v>9</v>
+        <v>9999</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="E8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1">
-        <v>10</v>
-      </c>
-      <c r="K8" s="1">
-        <v>2309</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1301</v>
-      </c>
-      <c r="M8" s="1">
-        <v>400</v>
-      </c>
-      <c r="N8" s="1">
-        <v>100</v>
-      </c>
-      <c r="O8" s="1">
-        <v>60</v>
-      </c>
-      <c r="P8" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="R8" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="S8" s="1">
-        <v>20</v>
-      </c>
-      <c r="T8" s="1">
-        <v>20</v>
-      </c>
-      <c r="U8" s="1">
-        <v>3</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0.15</v>
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="W8" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
       </c>
-      <c r="Y8" s="1">
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:30">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1">
         <v>0</v>
       </c>
-      <c r="Z8" s="1">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="AA8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>12</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>13</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>14</v>
-      </c>
-      <c r="AE8" s="1">
-        <v>2</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" ht="12" customHeight="1" spans="1:32">
-      <c r="B9">
-        <v>1001</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
+      <c r="T9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="W9" s="1">
         <v>0</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
+      <c r="X9" s="1">
         <v>0</v>
       </c>
-      <c r="K9">
-        <v>2101</v>
-      </c>
-      <c r="L9">
-        <v>1105</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC9" s="1">
         <v>0</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>10</v>
-      </c>
-      <c r="Q9">
-        <v>0.5</v>
-      </c>
-      <c r="R9">
-        <v>6</v>
-      </c>
-      <c r="S9">
-        <v>20</v>
-      </c>
-      <c r="T9">
-        <v>20</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0.15</v>
-      </c>
-      <c r="W9">
-        <v>1.5</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>77</v>
+      <c r="AD9" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="123">
   <si>
     <t>#</t>
   </si>
@@ -2125,9 +2125,7 @@
       <c r="AC9" s="1">
         <v>0</v>
       </c>
-      <c r="AD9" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="AD9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="128">
   <si>
     <t>#</t>
   </si>
@@ -59,6 +59,9 @@
     <t>IconId</t>
   </si>
   <si>
+    <t>HeadImgId</t>
+  </si>
+  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -161,7 +164,10 @@
     <t>棋子预制体资源ID（阶级数组，暂时三阶相同）</t>
   </si>
   <si>
-    <t>UI图标资源ID（阶级数组，暂时三阶相同）</t>
+    <t>棋子图标资源ID（阶级数组，暂时三阶相同）</t>
+  </si>
+  <si>
+    <t>棋子头像资源ID（阶级数组，暂时三阶相同）</t>
   </si>
   <si>
     <t>最大生命值（三个阶级）</t>
@@ -236,7 +242,10 @@
     <t>1301,1301,1301</t>
   </si>
   <si>
-    <t>400,580,800</t>
+    <t>13001,13001,13001</t>
+  </si>
+  <si>
+    <t>4000,580,800</t>
   </si>
   <si>
     <t>100,100,100</t>
@@ -293,7 +302,10 @@
     <t>1304,1304,1304</t>
   </si>
   <si>
-    <t>300,420,580</t>
+    <t>13004,13004,13004</t>
+  </si>
+  <si>
+    <t>3000,420,580</t>
   </si>
   <si>
     <t>1000,1000,1000</t>
@@ -344,7 +356,7 @@
     <t>2309,2309,2309</t>
   </si>
   <si>
-    <t>400,400,400</t>
+    <t>4000,400,400</t>
   </si>
   <si>
     <t>10,10,10</t>
@@ -363,6 +375,9 @@
   </si>
   <si>
     <t>1399,1399,1399</t>
+  </si>
+  <si>
+    <t>13999,13999,13999</t>
   </si>
   <si>
     <t>2000,2000,2000</t>
@@ -1363,8 +1378,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AE9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1375,25 +1390,25 @@
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
-    <col min="11" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="16" width="22" customWidth="1"/>
-    <col min="17" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="20" customWidth="1"/>
-    <col min="21" max="21" width="26" customWidth="1"/>
-    <col min="22" max="22" width="22" customWidth="1"/>
-    <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="26" width="36" customWidth="1"/>
-    <col min="27" max="27" width="30" customWidth="1"/>
-    <col min="28" max="28" width="28" customWidth="1"/>
-    <col min="29" max="29" width="41" customWidth="1"/>
-    <col min="30" max="30" width="42" customWidth="1"/>
+    <col min="10" max="11" width="40" customWidth="1"/>
+    <col min="12" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="17" width="22" customWidth="1"/>
+    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="26" max="27" width="36" customWidth="1"/>
+    <col min="28" max="28" width="30" customWidth="1"/>
+    <col min="29" max="29" width="28" customWidth="1"/>
+    <col min="30" max="30" width="41" customWidth="1"/>
+    <col min="31" max="31" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,20 +1431,21 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="1"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
-      <c r="W1" s="1"/>
+      <c r="W1" s="2"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="2"/>
+      <c r="Y1" s="1"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="2"/>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,10 +1498,10 @@
       <c r="R2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U2" s="2" t="s">
@@ -1494,13 +1510,13 @@
       <c r="V2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="Z2" s="2" t="s">
@@ -1512,203 +1528,212 @@
       <c r="AB2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="AE2" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>35</v>
+      <c r="AD3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" ht="28.8" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="T4" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="U4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="W4" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="W4" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="X4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y4" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="Y4" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="Z4" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="AD4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:30">
+    <row r="5" ht="15" customHeight="1" spans="1:31">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -1717,86 +1742,89 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="S5" s="1">
+        <v>78</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="T5" s="1">
         <v>3</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="U5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
       </c>
-      <c r="Y5" s="2" t="s">
-        <v>79</v>
+      <c r="Y5" s="1">
+        <v>0</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC5" s="1">
+        <v>84</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD5" s="1">
         <v>2</v>
       </c>
-      <c r="AD5" s="2" t="s">
-        <v>83</v>
+      <c r="AE5" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:30">
+    <row r="6" ht="15" customHeight="1" spans="1:31">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1805,86 +1833,89 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S6" s="1">
+        <v>98</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="T6" s="1">
         <v>3</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="U6" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>99</v>
+      <c r="Y6" s="1">
+        <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AC6" s="1">
+        <v>105</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD6" s="1">
         <v>2</v>
       </c>
-      <c r="AD6" s="2" t="s">
-        <v>83</v>
+      <c r="AE6" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:30">
+    <row r="7" ht="15" customHeight="1" spans="1:31">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>9</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1893,86 +1924,89 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="S7" s="1">
+        <v>112</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T7" s="1">
         <v>3</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="U7" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W7" s="1">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>79</v>
+      <c r="Y7" s="1">
+        <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC7" s="1">
+        <v>84</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD7" s="1">
         <v>2</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>83</v>
+      <c r="AE7" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:30">
+    <row r="8" ht="15" customHeight="1" spans="1:31">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>9999</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1983,78 +2017,81 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="S8" s="1">
+        <v>81</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="U8" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="W8" s="1">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
       </c>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2"/>
       <c r="AA8" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC8" s="1">
+        <v>118</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD8" s="1">
         <v>3</v>
       </c>
-      <c r="AD8" s="2" t="s">
-        <v>83</v>
+      <c r="AE8" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:30">
+    <row r="9" ht="15" customHeight="1" spans="1:31">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1001</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2065,67 +2102,70 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="W9" s="1">
-        <v>0</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
       </c>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2" t="s">
-        <v>113</v>
-      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2"/>
       <c r="AA9" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC9" s="1">
+        <v>118</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD9" s="1">
         <v>0</v>
       </c>
-      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="27948" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="145">
   <si>
     <t>#</t>
   </si>
@@ -366,6 +366,57 @@
   </si>
   <si>
     <t>20,20,20</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2310,2310,2310</t>
+  </si>
+  <si>
+    <t>1310,1310,1310</t>
+  </si>
+  <si>
+    <t>13010,13010,13010</t>
+  </si>
+  <si>
+    <t>1800,2500,3500</t>
+  </si>
+  <si>
+    <t>12,18,28</t>
+  </si>
+  <si>
+    <t>0.8,0.9,1.0</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>15,20,28</t>
+  </si>
+  <si>
+    <t>10,15,20</t>
+  </si>
+  <si>
+    <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>31,31,31</t>
+  </si>
+  <si>
+    <t>32,32,32</t>
+  </si>
+  <si>
+    <t>33,33,33</t>
+  </si>
+  <si>
+    <t>34,34,34</t>
+  </si>
+  <si>
+    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
   </si>
   <si>
     <t>稻草人</t>
@@ -423,7 +474,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -879,148 +937,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1378,7 +1436,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1390,7 +1448,7 @@
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
-    <col min="10" max="11" width="40" customWidth="1"/>
+    <col min="10" max="11" width="42" customWidth="1"/>
     <col min="12" max="14" width="24" customWidth="1"/>
     <col min="15" max="15" width="20" customWidth="1"/>
     <col min="16" max="17" width="22" customWidth="1"/>
@@ -1405,7 +1463,7 @@
     <col min="28" max="28" width="30" customWidth="1"/>
     <col min="29" max="29" width="28" customWidth="1"/>
     <col min="30" max="30" width="41" customWidth="1"/>
-    <col min="31" max="31" width="42" customWidth="1"/>
+    <col min="31" max="31" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -1631,7 +1689,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:31">
+    <row r="4" spans="1:31">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2002,7 +2060,7 @@
     <row r="8" ht="15" customHeight="1" spans="1:31">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
-        <v>9999</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -2012,21 +2070,23 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>73</v>
@@ -2035,25 +2095,25 @@
         <v>81</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="T8" s="1">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>101</v>
@@ -2067,34 +2127,36 @@
       <c r="Y8" s="1">
         <v>0</v>
       </c>
-      <c r="Z8" s="2"/>
+      <c r="Z8" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="AA8" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AD8" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:31">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
-        <v>1001</v>
+        <v>9999</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -2102,49 +2164,49 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="T9" s="1">
         <v>0</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -2154,18 +2216,103 @@
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="AD9" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:31">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="AE9" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12300"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="146">
   <si>
     <t>#</t>
   </si>
@@ -245,7 +245,7 @@
     <t>13001,13001,13001</t>
   </si>
   <si>
-    <t>4000,580,800</t>
+    <t>400,580,800</t>
   </si>
   <si>
     <t>100,100,100</t>
@@ -305,16 +305,16 @@
     <t>13004,13004,13004</t>
   </si>
   <si>
-    <t>3000,420,580</t>
-  </si>
-  <si>
-    <t>1000,1000,1000</t>
+    <t>300,420,580</t>
+  </si>
+  <si>
+    <t>120,120,120</t>
   </si>
   <si>
     <t>80,80,80</t>
   </si>
   <si>
-    <t>5,7,10</t>
+    <t>8,12,20</t>
   </si>
   <si>
     <t>1,1,1</t>
@@ -356,7 +356,7 @@
     <t>2309,2309,2309</t>
   </si>
   <si>
-    <t>4000,400,400</t>
+    <t>400,400,400</t>
   </si>
   <si>
     <t>10,10,10</t>
@@ -383,7 +383,7 @@
     <t>13010,13010,13010</t>
   </si>
   <si>
-    <t>1800,2500,3500</t>
+    <t>320,450,600</t>
   </si>
   <si>
     <t>12,18,28</t>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>10,20,30</t>
   </si>
   <si>
     <t>31,31,31</t>
@@ -474,14 +477,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -937,148 +933,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2092,7 +2088,7 @@
         <v>73</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>119</v>
@@ -2119,7 +2115,7 @@
         <v>101</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2128,22 +2124,22 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AD8" s="1">
         <v>1</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:31">
@@ -2153,7 +2149,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2164,16 +2160,16 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>73</v>
@@ -2216,13 +2212,13 @@
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD9" s="1">
         <v>3</v>
@@ -2238,7 +2234,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -2249,49 +2245,49 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>68</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="T10" s="1">
         <v>0</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
@@ -2301,13 +2297,13 @@
       </c>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD10" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1433,7 +1433,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AE10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2237,7 +2237,7 @@
         <v>137</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -335,7 +335,7 @@
     <t>1.5,1.5,1.5</t>
   </si>
   <si>
-    <t>15,28,45</t>
+    <t>1,28,45</t>
   </si>
   <si>
     <t>21,21,21</t>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -119,6 +119,9 @@
     <t>AIType</t>
   </si>
   <si>
+    <t>CustomData</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -227,6 +230,9 @@
     <t>棋子AI模式:1=近战寻敌2=远程站桩3=稻草人</t>
   </si>
   <si>
+    <t>自定义数据（JSON格式）</t>
+  </si>
+  <si>
     <t>棋子的背景描述（三个值：一阶/二阶/三阶）</t>
   </si>
   <si>
@@ -335,7 +341,7 @@
     <t>1.5,1.5,1.5</t>
   </si>
   <si>
-    <t>1,28,45</t>
+    <t>16,28,45</t>
   </si>
   <si>
     <t>21,21,21</t>
@@ -365,6 +371,9 @@
     <t>0.5,0.5,0.5</t>
   </si>
   <si>
+    <t>10,20,20</t>
+  </si>
+  <si>
     <t>20,20,20</t>
   </si>
   <si>
@@ -420,6 +429,114 @@
   </si>
   <si>
     <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>恶魂</t>
+  </si>
+  <si>
+    <t>2311,2311,2311</t>
+  </si>
+  <si>
+    <t>1311,1311,1311</t>
+  </si>
+  <si>
+    <t>13011,13011,13011</t>
+  </si>
+  <si>
+    <t>280,400,550</t>
+  </si>
+  <si>
+    <t>9,14,22</t>
+  </si>
+  <si>
+    <t>20,15,20</t>
+  </si>
+  <si>
+    <t>35,50,70</t>
+  </si>
+  <si>
+    <t>41,41,41</t>
+  </si>
+  <si>
+    <t>42,42,42</t>
+  </si>
+  <si>
+    <t>43,43,43</t>
+  </si>
+  <si>
+    <t>44,44,44</t>
+  </si>
+  <si>
+    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗杨戬</t>
+  </si>
+  <si>
+    <t>2312,2312,2312</t>
+  </si>
+  <si>
+    <t>13012,13012,13012</t>
+  </si>
+  <si>
+    <t>800,1200,1600</t>
+  </si>
+  <si>
+    <t>150,150,150</t>
+  </si>
+  <si>
+    <t>25,40,60</t>
+  </si>
+  <si>
+    <t>0.6,0.75,0.9</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>40,50,60</t>
+  </si>
+  <si>
+    <t>30,40,50</t>
+  </si>
+  <si>
+    <t>0.2,0.25,0.3</t>
+  </si>
+  <si>
+    <t>2.0,2.2,2.5</t>
+  </si>
+  <si>
+    <t>51,51,51</t>
+  </si>
+  <si>
+    <t>52,52,52</t>
+  </si>
+  <si>
+    <t>53,53,53</t>
+  </si>
+  <si>
+    <t>55,55,55</t>
+  </si>
+  <si>
+    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
+  </si>
+  <si>
+    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗哮天犬</t>
+  </si>
+  <si>
+    <t>2313,2313,2313</t>
+  </si>
+  <si>
+    <t>13013,13013,13013</t>
+  </si>
+  <si>
+    <t>56,56,56</t>
+  </si>
+  <si>
+    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
   </si>
   <si>
     <t>稻草人</t>
@@ -477,7 +594,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,148 +1057,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1432,7 +1556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1459,10 +1583,10 @@
     <col min="28" max="28" width="30" customWidth="1"/>
     <col min="29" max="29" width="28" customWidth="1"/>
     <col min="30" max="30" width="41" customWidth="1"/>
-    <col min="31" max="31" width="50" customWidth="1"/>
+    <col min="31" max="32" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1497,9 +1621,10 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="2"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="2"/>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1588,206 +1713,215 @@
       <c r="AD2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="AF2" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>36</v>
+      <c r="AF3" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE4" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="AE4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:31">
+    <row r="5" ht="15" customHeight="1" spans="1:32">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -1796,55 +1930,55 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="T5" s="1">
         <v>3</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
@@ -1853,32 +1987,33 @@
         <v>0</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AD5" s="1">
         <v>2</v>
       </c>
-      <c r="AE5" s="2" t="s">
-        <v>86</v>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:31">
+    <row r="6" ht="15" customHeight="1" spans="1:32">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1887,55 +2022,55 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T6" s="1">
         <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -1944,32 +2079,33 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AD6" s="1">
         <v>2</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>86</v>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:31">
+    <row r="7" ht="15" customHeight="1" spans="1:32">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>9</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -1978,55 +2114,55 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="T7" s="1">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2035,32 +2171,33 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AD7" s="1">
         <v>2</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>86</v>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:31">
+    <row r="8" ht="15" customHeight="1" spans="1:32">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2070,52 +2207,52 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2124,85 +2261,88 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AD8" s="1">
         <v>1</v>
       </c>
-      <c r="AE8" s="2" t="s">
-        <v>130</v>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:31">
+    <row r="9" ht="15" customHeight="1" spans="1:32">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
-        <v>9999</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="I9" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="T9" s="1">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -2210,84 +2350,89 @@
       <c r="Y9" s="1">
         <v>0</v>
       </c>
-      <c r="Z9" s="2"/>
+      <c r="Z9" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="AA9" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="AD9" s="1">
-        <v>3</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>86</v>
+        <v>2</v>
+      </c>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="2" t="s">
+        <v>146</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:31">
+    <row r="10" ht="15" customHeight="1" spans="1:32">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
-        <v>1001</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="I10" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="T10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
@@ -2295,20 +2440,328 @@
       <c r="Y10" s="1">
         <v>0</v>
       </c>
-      <c r="Z10" s="2"/>
+      <c r="Z10" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="AA10" s="2" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="AD10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:32">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="AE10" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T11" s="1">
+        <v>4</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:32">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>9999</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>3</v>
+      </c>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:32">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1"/>
+      <c r="AF13" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15" spans="1:32">
+      <c r="AE15" s="1"/>
+    </row>
+    <row r="16" spans="1:32">
+      <c r="AE16" s="1"/>
+    </row>
+    <row r="17" spans="31:31">
+      <c r="AE17" s="1"/>
+    </row>
+    <row r="18" spans="31:31">
+      <c r="AE18" s="1"/>
+    </row>
+    <row r="19" spans="31:31">
+      <c r="AE19" s="1"/>
+    </row>
+    <row r="20" spans="31:31">
+      <c r="AE20" s="1"/>
+    </row>
+    <row r="21" spans="31:31">
+      <c r="AE21" s="1"/>
+    </row>
+    <row r="22" spans="31:31">
+      <c r="AE22" s="1"/>
+    </row>
+    <row r="23" spans="31:31">
+      <c r="AE23" s="1"/>
+    </row>
+    <row r="24" spans="31:31">
+      <c r="AE24" s="1"/>
+    </row>
+    <row r="25" spans="31:31">
+      <c r="AE25" s="1"/>
+    </row>
+    <row r="26" spans="31:31">
+      <c r="AE26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="186">
   <si>
     <t>#</t>
   </si>
@@ -173,7 +173,8 @@
     <t>棋子头像资源ID（阶级数组，暂时三阶相同）</t>
   </si>
   <si>
-    <t>最大生命值（三个阶级）</t>
+    <t>最大生命值（三个阶级）
+**基础属性**</t>
   </si>
   <si>
     <t>最大法力值（三个阶级）</t>
@@ -182,7 +183,8 @@
     <t>初始法力值（三个阶级）</t>
   </si>
   <si>
-    <t>攻击力（三个阶级）</t>
+    <t>攻击力（三个阶级）
+**基础属性**</t>
   </si>
   <si>
     <t>攻击速度（三个阶级）</t>
@@ -191,10 +193,12 @@
     <t>攻击距离（三个阶级）</t>
   </si>
   <si>
-    <t>护甲（三个阶级）</t>
-  </si>
-  <si>
-    <t>魔抗（三个阶级）</t>
+    <t>护甲（三个阶级）
+**基础属性**</t>
+  </si>
+  <si>
+    <t>魔抗（三个阶级）
+**基础属性**</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -206,7 +210,8 @@
     <t>暴击伤害倍率（三个阶级）</t>
   </si>
   <si>
-    <t>法术强度（三个阶级）</t>
+    <t>法术强度（三个阶级）
+**基础属性**</t>
   </si>
   <si>
     <t>护盾值</t>
@@ -311,178 +316,181 @@
     <t>13004,13004,13004</t>
   </si>
   <si>
-    <t>300,420,580</t>
+    <t>30,420,580</t>
   </si>
   <si>
     <t>120,120,120</t>
   </si>
   <si>
+    <t>0,80,80</t>
+  </si>
+  <si>
+    <t>8,12,20</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>10,12,15</t>
+  </si>
+  <si>
+    <t>25,35,45</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>16,28,45</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>敌人测试</t>
+  </si>
+  <si>
+    <t>2309,2309,2309</t>
+  </si>
+  <si>
+    <t>400,400,400</t>
+  </si>
+  <si>
+    <t>10,10,10</t>
+  </si>
+  <si>
+    <t>0.5,0.5,0.5</t>
+  </si>
+  <si>
+    <t>10,20,20</t>
+  </si>
+  <si>
+    <t>20,20,20</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2310,2310,2310</t>
+  </si>
+  <si>
+    <t>1310,1310,1310</t>
+  </si>
+  <si>
+    <t>13010,13010,13010</t>
+  </si>
+  <si>
+    <t>320,450,600</t>
+  </si>
+  <si>
+    <t>12,18,28</t>
+  </si>
+  <si>
+    <t>0.8,0.9,1.0</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>15,20,28</t>
+  </si>
+  <si>
+    <t>10,15,20</t>
+  </si>
+  <si>
+    <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>10,20,30</t>
+  </si>
+  <si>
+    <t>31,31,31</t>
+  </si>
+  <si>
+    <t>32,32,32</t>
+  </si>
+  <si>
+    <t>33,33,33</t>
+  </si>
+  <si>
+    <t>34,34,34</t>
+  </si>
+  <si>
+    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>恶魂</t>
+  </si>
+  <si>
+    <t>2311,2311,2311</t>
+  </si>
+  <si>
+    <t>1311,1311,1311</t>
+  </si>
+  <si>
+    <t>13011,13011,13011</t>
+  </si>
+  <si>
+    <t>280,400,550</t>
+  </si>
+  <si>
+    <t>9,14,22</t>
+  </si>
+  <si>
+    <t>20,15,20</t>
+  </si>
+  <si>
+    <t>35,50,70</t>
+  </si>
+  <si>
+    <t>41,41,41</t>
+  </si>
+  <si>
+    <t>42,42,42</t>
+  </si>
+  <si>
+    <t>43,43,43</t>
+  </si>
+  <si>
+    <t>44,44,44</t>
+  </si>
+  <si>
+    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗杨戬</t>
+  </si>
+  <si>
+    <t>2312,2312,2312</t>
+  </si>
+  <si>
+    <t>13012,13012,13012</t>
+  </si>
+  <si>
+    <t>800,1200,1600</t>
+  </si>
+  <si>
+    <t>150,150,150</t>
+  </si>
+  <si>
     <t>80,80,80</t>
-  </si>
-  <si>
-    <t>8,12,20</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
-  </si>
-  <si>
-    <t>8,9,10</t>
-  </si>
-  <si>
-    <t>10,12,15</t>
-  </si>
-  <si>
-    <t>25,35,45</t>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-  </si>
-  <si>
-    <t>1.5,1.5,1.5</t>
-  </si>
-  <si>
-    <t>16,28,45</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>22,22,22</t>
-  </si>
-  <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>24,24,24</t>
-  </si>
-  <si>
-    <t>敌人测试</t>
-  </si>
-  <si>
-    <t>2309,2309,2309</t>
-  </si>
-  <si>
-    <t>400,400,400</t>
-  </si>
-  <si>
-    <t>10,10,10</t>
-  </si>
-  <si>
-    <t>0.5,0.5,0.5</t>
-  </si>
-  <si>
-    <t>10,20,20</t>
-  </si>
-  <si>
-    <t>20,20,20</t>
-  </si>
-  <si>
-    <t>邪灵</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2310,2310,2310</t>
-  </si>
-  <si>
-    <t>1310,1310,1310</t>
-  </si>
-  <si>
-    <t>13010,13010,13010</t>
-  </si>
-  <si>
-    <t>320,450,600</t>
-  </si>
-  <si>
-    <t>12,18,28</t>
-  </si>
-  <si>
-    <t>0.8,0.9,1.0</t>
-  </si>
-  <si>
-    <t>2,2,2</t>
-  </si>
-  <si>
-    <t>15,20,28</t>
-  </si>
-  <si>
-    <t>10,15,20</t>
-  </si>
-  <si>
-    <t>0.05,0.05,0.05</t>
-  </si>
-  <si>
-    <t>10,20,30</t>
-  </si>
-  <si>
-    <t>31,31,31</t>
-  </si>
-  <si>
-    <t>32,32,32</t>
-  </si>
-  <si>
-    <t>33,33,33</t>
-  </si>
-  <si>
-    <t>34,34,34</t>
-  </si>
-  <si>
-    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>恶魂</t>
-  </si>
-  <si>
-    <t>2311,2311,2311</t>
-  </si>
-  <si>
-    <t>1311,1311,1311</t>
-  </si>
-  <si>
-    <t>13011,13011,13011</t>
-  </si>
-  <si>
-    <t>280,400,550</t>
-  </si>
-  <si>
-    <t>9,14,22</t>
-  </si>
-  <si>
-    <t>20,15,20</t>
-  </si>
-  <si>
-    <t>35,50,70</t>
-  </si>
-  <si>
-    <t>41,41,41</t>
-  </si>
-  <si>
-    <t>42,42,42</t>
-  </si>
-  <si>
-    <t>43,43,43</t>
-  </si>
-  <si>
-    <t>44,44,44</t>
-  </si>
-  <si>
-    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗杨戬</t>
-  </si>
-  <si>
-    <t>2312,2312,2312</t>
-  </si>
-  <si>
-    <t>13012,13012,13012</t>
-  </si>
-  <si>
-    <t>800,1200,1600</t>
-  </si>
-  <si>
-    <t>150,150,150</t>
   </si>
   <si>
     <t>25,40,60</t>
@@ -1816,7 +1824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" ht="27" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2405,31 +2413,31 @@
         <v>151</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T10" s="1">
         <v>2</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>83</v>
@@ -2441,25 +2449,25 @@
         <v>0</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AD10" s="1">
         <v>1</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:32">
@@ -2469,7 +2477,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2482,13 +2490,13 @@
         <v>70</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>83</v>
@@ -2536,7 +2544,7 @@
         <v>83</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>83</v>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:32">
@@ -2559,7 +2567,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2570,16 +2578,16 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>75</v>
@@ -2622,13 +2630,13 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AD12" s="1">
         <v>3</v>
@@ -2645,7 +2653,7 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
@@ -2656,49 +2664,49 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
@@ -2708,13 +2716,13 @@
       </c>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="182">
   <si>
     <t>#</t>
   </si>
@@ -152,7 +152,7 @@
     <t>棋子名称</t>
   </si>
   <si>
-    <t>品质/等级（1-4，对应蓝、紫、金、炫彩）</t>
+    <t>品质（1-4，对应蓝、紫、金、炫彩）</t>
   </si>
   <si>
     <t>占用人口数</t>
@@ -173,18 +173,16 @@
     <t>棋子头像资源ID（阶级数组，暂时三阶相同）</t>
   </si>
   <si>
-    <t>最大生命值（三个阶级）
-**基础属性**</t>
-  </si>
-  <si>
-    <t>最大法力值（三个阶级）</t>
+    <t>最大生命值（三个阶级）**基础属性**</t>
+  </si>
+  <si>
+    <t>最大法力值（三个阶级）**基础属性**</t>
   </si>
   <si>
     <t>初始法力值（三个阶级）</t>
   </si>
   <si>
-    <t>攻击力（三个阶级）
-**基础属性**</t>
+    <t>攻击力（三个阶级）**基础属性**</t>
   </si>
   <si>
     <t>攻击速度（三个阶级）</t>
@@ -193,12 +191,10 @@
     <t>攻击距离（三个阶级）</t>
   </si>
   <si>
-    <t>护甲（三个阶级）
-**基础属性**</t>
-  </si>
-  <si>
-    <t>魔抗（三个阶级）
-**基础属性**</t>
+    <t>护甲（三个阶级）**基础属性**</t>
+  </si>
+  <si>
+    <t>魔抗（三个阶级）**基础属性**</t>
   </si>
   <si>
     <t>移动速度</t>
@@ -210,8 +206,7 @@
     <t>暴击伤害倍率（三个阶级）</t>
   </si>
   <si>
-    <t>法术强度（三个阶级）
-**基础属性**</t>
+    <t>法术强度（三个阶级）**基础属性**</t>
   </si>
   <si>
     <t>护盾值</t>
@@ -256,310 +251,298 @@
     <t>13001,13001,13001</t>
   </si>
   <si>
-    <t>400,580,800</t>
+    <t>400,640,960</t>
+  </si>
+  <si>
+    <t>100,160,240</t>
+  </si>
+  <si>
+    <t>60,60,60</t>
+  </si>
+  <si>
+    <t>10,16,24</t>
+  </si>
+  <si>
+    <t>0.5,0.8,1.2</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>18,29,43</t>
+  </si>
+  <si>
+    <t>13,21,31</t>
+  </si>
+  <si>
+    <t>0.15,0.2,0.25</t>
+  </si>
+  <si>
+    <t>1.5,1.7,2.0</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>11,11,11</t>
+  </si>
+  <si>
+    <t>12,12,12</t>
+  </si>
+  <si>
+    <t>13,13,13</t>
+  </si>
+  <si>
+    <t>14,14,14</t>
+  </si>
+  <si>
+    <t>暂无,暂无,暂无</t>
+  </si>
+  <si>
+    <t>嫦娥</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2304,2304,2304</t>
+  </si>
+  <si>
+    <t>1304,1304,1304</t>
+  </si>
+  <si>
+    <t>13004,13004,13004</t>
+  </si>
+  <si>
+    <t>330,528,792</t>
+  </si>
+  <si>
+    <t>180,288,432</t>
+  </si>
+  <si>
+    <t>80,80,80</t>
+  </si>
+  <si>
+    <t>0.8,0.8,0.8</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>15,24,36</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>50,80,120</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>敌人测试</t>
+  </si>
+  <si>
+    <t>2309,2309,2309</t>
+  </si>
+  <si>
+    <t>400,400,400</t>
   </si>
   <si>
     <t>100,100,100</t>
   </si>
   <si>
-    <t>60,60,60</t>
-  </si>
-  <si>
-    <t>10,16,26</t>
-  </si>
-  <si>
-    <t>0.5,0.65,0.8</t>
-  </si>
-  <si>
-    <t>10,11,12</t>
-  </si>
-  <si>
-    <t>20,25,30</t>
-  </si>
-  <si>
-    <t>0.15,0.2,0.25</t>
-  </si>
-  <si>
-    <t>1.5,1.7,2.0</t>
-  </si>
-  <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>11,11,11</t>
-  </si>
-  <si>
-    <t>12,12,12</t>
-  </si>
-  <si>
-    <t>13,13,13</t>
-  </si>
-  <si>
-    <t>14,14,14</t>
-  </si>
-  <si>
-    <t>暂无,暂无,暂无</t>
-  </si>
-  <si>
-    <t>嫦娥</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2304,2304,2304</t>
-  </si>
-  <si>
-    <t>1304,1304,1304</t>
-  </si>
-  <si>
-    <t>13004,13004,13004</t>
-  </si>
-  <si>
-    <t>30,420,580</t>
-  </si>
-  <si>
-    <t>120,120,120</t>
-  </si>
-  <si>
-    <t>0,80,80</t>
-  </si>
-  <si>
-    <t>8,12,20</t>
+    <t>10,10,10</t>
+  </si>
+  <si>
+    <t>0.5,0.5,0.5</t>
+  </si>
+  <si>
+    <t>10,20,20</t>
+  </si>
+  <si>
+    <t>20,20,20</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2310,2310,2310</t>
+  </si>
+  <si>
+    <t>1310,1310,1310</t>
+  </si>
+  <si>
+    <t>13010,13010,13010</t>
+  </si>
+  <si>
+    <t>240,384,576</t>
+  </si>
+  <si>
+    <t>160,256,384</t>
+  </si>
+  <si>
+    <t>0.8,1.28,1.92</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>6,10,14</t>
+  </si>
+  <si>
+    <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>60,96,144</t>
+  </si>
+  <si>
+    <t>31,31,31</t>
+  </si>
+  <si>
+    <t>32,32,32</t>
+  </si>
+  <si>
+    <t>33,33,33</t>
+  </si>
+  <si>
+    <t>34,34,34</t>
+  </si>
+  <si>
+    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>恶魂</t>
+  </si>
+  <si>
+    <t>2311,2311,2311</t>
+  </si>
+  <si>
+    <t>1311,1311,1311</t>
+  </si>
+  <si>
+    <t>13011,13011,13011</t>
+  </si>
+  <si>
+    <t>16,26,38</t>
+  </si>
+  <si>
+    <t>44,70,106</t>
+  </si>
+  <si>
+    <t>41,41,41</t>
+  </si>
+  <si>
+    <t>42,42,42</t>
+  </si>
+  <si>
+    <t>43,43,43</t>
+  </si>
+  <si>
+    <t>44,44,44</t>
+  </si>
+  <si>
+    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗杨戬</t>
+  </si>
+  <si>
+    <t>2312,2312,2312</t>
+  </si>
+  <si>
+    <t>13012,13012,13012</t>
+  </si>
+  <si>
+    <t>1008,1613,2419</t>
+  </si>
+  <si>
+    <t>72,115,172</t>
+  </si>
+  <si>
+    <t>20,32,48</t>
+  </si>
+  <si>
+    <t>0.6,0.96,1.44</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>36,58,86</t>
+  </si>
+  <si>
+    <t>0.2,0.25,0.3</t>
+  </si>
+  <si>
+    <t>2.0,2.2,2.5</t>
+  </si>
+  <si>
+    <t>51,51,51</t>
+  </si>
+  <si>
+    <t>52,52,52</t>
+  </si>
+  <si>
+    <t>53,53,53</t>
+  </si>
+  <si>
+    <t>55,55,55</t>
+  </si>
+  <si>
+    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
+  </si>
+  <si>
+    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗哮天犬</t>
+  </si>
+  <si>
+    <t>2313,2313,2313</t>
+  </si>
+  <si>
+    <t>13013,13013,13013</t>
+  </si>
+  <si>
+    <t>56,56,56</t>
+  </si>
+  <si>
+    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>稻草人</t>
+  </si>
+  <si>
+    <t>2399,2399,2399</t>
+  </si>
+  <si>
+    <t>1399,1399,1399</t>
+  </si>
+  <si>
+    <t>13999,13999,13999</t>
+  </si>
+  <si>
+    <t>2000,2000,2000</t>
   </si>
   <si>
     <t>1,1,1</t>
-  </si>
-  <si>
-    <t>8,9,10</t>
-  </si>
-  <si>
-    <t>10,12,15</t>
-  </si>
-  <si>
-    <t>25,35,45</t>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-  </si>
-  <si>
-    <t>1.5,1.5,1.5</t>
-  </si>
-  <si>
-    <t>16,28,45</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>22,22,22</t>
-  </si>
-  <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>24,24,24</t>
-  </si>
-  <si>
-    <t>敌人测试</t>
-  </si>
-  <si>
-    <t>2309,2309,2309</t>
-  </si>
-  <si>
-    <t>400,400,400</t>
-  </si>
-  <si>
-    <t>10,10,10</t>
-  </si>
-  <si>
-    <t>0.5,0.5,0.5</t>
-  </si>
-  <si>
-    <t>10,20,20</t>
-  </si>
-  <si>
-    <t>20,20,20</t>
-  </si>
-  <si>
-    <t>邪灵</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2310,2310,2310</t>
-  </si>
-  <si>
-    <t>1310,1310,1310</t>
-  </si>
-  <si>
-    <t>13010,13010,13010</t>
-  </si>
-  <si>
-    <t>320,450,600</t>
-  </si>
-  <si>
-    <t>12,18,28</t>
-  </si>
-  <si>
-    <t>0.8,0.9,1.0</t>
-  </si>
-  <si>
-    <t>2,2,2</t>
-  </si>
-  <si>
-    <t>15,20,28</t>
-  </si>
-  <si>
-    <t>10,15,20</t>
-  </si>
-  <si>
-    <t>0.05,0.05,0.05</t>
-  </si>
-  <si>
-    <t>10,20,30</t>
-  </si>
-  <si>
-    <t>31,31,31</t>
-  </si>
-  <si>
-    <t>32,32,32</t>
-  </si>
-  <si>
-    <t>33,33,33</t>
-  </si>
-  <si>
-    <t>34,34,34</t>
-  </si>
-  <si>
-    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>恶魂</t>
-  </si>
-  <si>
-    <t>2311,2311,2311</t>
-  </si>
-  <si>
-    <t>1311,1311,1311</t>
-  </si>
-  <si>
-    <t>13011,13011,13011</t>
-  </si>
-  <si>
-    <t>280,400,550</t>
-  </si>
-  <si>
-    <t>9,14,22</t>
-  </si>
-  <si>
-    <t>20,15,20</t>
-  </si>
-  <si>
-    <t>35,50,70</t>
-  </si>
-  <si>
-    <t>41,41,41</t>
-  </si>
-  <si>
-    <t>42,42,42</t>
-  </si>
-  <si>
-    <t>43,43,43</t>
-  </si>
-  <si>
-    <t>44,44,44</t>
-  </si>
-  <si>
-    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗杨戬</t>
-  </si>
-  <si>
-    <t>2312,2312,2312</t>
-  </si>
-  <si>
-    <t>13012,13012,13012</t>
-  </si>
-  <si>
-    <t>800,1200,1600</t>
-  </si>
-  <si>
-    <t>150,150,150</t>
-  </si>
-  <si>
-    <t>80,80,80</t>
-  </si>
-  <si>
-    <t>25,40,60</t>
-  </si>
-  <si>
-    <t>0.6,0.75,0.9</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>40,50,60</t>
-  </si>
-  <si>
-    <t>30,40,50</t>
-  </si>
-  <si>
-    <t>0.2,0.25,0.3</t>
-  </si>
-  <si>
-    <t>2.0,2.2,2.5</t>
-  </si>
-  <si>
-    <t>51,51,51</t>
-  </si>
-  <si>
-    <t>52,52,52</t>
-  </si>
-  <si>
-    <t>53,53,53</t>
-  </si>
-  <si>
-    <t>55,55,55</t>
-  </si>
-  <si>
-    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
-  </si>
-  <si>
-    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗哮天犬</t>
-  </si>
-  <si>
-    <t>2313,2313,2313</t>
-  </si>
-  <si>
-    <t>13013,13013,13013</t>
-  </si>
-  <si>
-    <t>56,56,56</t>
-  </si>
-  <si>
-    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>稻草人</t>
-  </si>
-  <si>
-    <t>2399,2399,2399</t>
-  </si>
-  <si>
-    <t>1399,1399,1399</t>
-  </si>
-  <si>
-    <t>13999,13999,13999</t>
-  </si>
-  <si>
-    <t>2000,2000,2000</t>
   </si>
   <si>
     <t>0</t>
@@ -1564,27 +1547,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF26"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
     <col min="10" max="11" width="42" customWidth="1"/>
-    <col min="12" max="14" width="24" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="12" max="13" width="36" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="15" max="15" width="32" customWidth="1"/>
     <col min="16" max="17" width="22" customWidth="1"/>
-    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="18" max="19" width="30" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
     <col min="21" max="21" width="20" customWidth="1"/>
     <col min="22" max="22" width="26" customWidth="1"/>
-    <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="23" max="23" width="34" customWidth="1"/>
     <col min="24" max="24" width="8" customWidth="1"/>
     <col min="25" max="25" width="16" customWidth="1"/>
     <col min="26" max="27" width="36" customWidth="1"/>
@@ -1824,7 +1808,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:32">
+    <row r="4" spans="1:32">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1974,19 +1958,19 @@
         <v>80</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T5" s="1">
         <v>3</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
@@ -1995,23 +1979,23 @@
         <v>0</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD5" s="1">
         <v>2</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:32">
@@ -2021,7 +2005,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -2033,28 +2017,28 @@
         <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>98</v>
@@ -2066,19 +2050,19 @@
         <v>100</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T6" s="1">
         <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -2087,23 +2071,23 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="AD6" s="1">
         <v>2</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:32">
@@ -2113,7 +2097,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -2128,7 +2112,7 @@
         <v>70</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>72</v>
@@ -2137,10 +2121,10 @@
         <v>73</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>76</v>
@@ -2164,13 +2148,13 @@
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="W7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2179,23 +2163,23 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD7" s="1">
         <v>2</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32">
@@ -2230,13 +2214,13 @@
         <v>121</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>76</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>123</v>
@@ -2248,19 +2232,19 @@
         <v>125</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2269,23 +2253,23 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA8" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="AD8" s="1">
         <v>1</v>
       </c>
       <c r="AE8" s="1"/>
       <c r="AF8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:32">
@@ -2295,7 +2279,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2308,25 +2292,25 @@
         <v>117</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="L9" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>76</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>123</v>
@@ -2335,22 +2319,22 @@
         <v>79</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="T9" s="1">
         <v>3.5</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -2359,23 +2343,23 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="AD9" s="1">
         <v>2</v>
       </c>
       <c r="AE9" s="1"/>
       <c r="AF9" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:32">
@@ -2385,7 +2369,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -2398,49 +2382,49 @@
         <v>70</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="N10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="R10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="T10" s="1">
         <v>2</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
@@ -2449,25 +2433,25 @@
         <v>0</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AD10" s="1">
         <v>1</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:32">
@@ -2477,7 +2461,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2490,49 +2474,49 @@
         <v>70</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T11" s="1">
         <v>4</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
@@ -2541,23 +2525,23 @@
         <v>0</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AD11" s="1">
         <v>1</v>
       </c>
       <c r="AE11" s="1"/>
-      <c r="AF11" s="1" t="s">
-        <v>170</v>
+      <c r="AF11" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:32">
@@ -2567,7 +2551,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2578,49 +2562,49 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -2630,20 +2614,20 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AD12" s="1">
         <v>3</v>
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:32">
@@ -2653,7 +2637,7 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
@@ -2664,49 +2648,49 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="M13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="P13" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="T13" s="1">
         <v>0</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
@@ -2716,60 +2700,21 @@
       </c>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AD13" s="1">
         <v>0</v>
       </c>
       <c r="AE13" s="1"/>
       <c r="AF13" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32">
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" spans="1:32">
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" spans="1:32">
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" spans="31:31">
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" spans="31:31">
-      <c r="AE18" s="1"/>
-    </row>
-    <row r="19" spans="31:31">
-      <c r="AE19" s="1"/>
-    </row>
-    <row r="20" spans="31:31">
-      <c r="AE20" s="1"/>
-    </row>
-    <row r="21" spans="31:31">
-      <c r="AE21" s="1"/>
-    </row>
-    <row r="22" spans="31:31">
-      <c r="AE22" s="1"/>
-    </row>
-    <row r="23" spans="31:31">
-      <c r="AE23" s="1"/>
-    </row>
-    <row r="24" spans="31:31">
-      <c r="AE24" s="1"/>
-    </row>
-    <row r="25" spans="31:31">
-      <c r="AE25" s="1"/>
-    </row>
-    <row r="26" spans="31:31">
-      <c r="AE26" s="1"/>
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="180">
   <si>
     <t>#</t>
   </si>
@@ -161,7 +161,7 @@
     <t>种族ID数组（用于触发羁绊，如：1,2）</t>
   </si>
   <si>
-    <t>职业ID数组（用于触发羁绊，如：3）</t>
+    <t>职业ID数组（用于触发羁绊，如：101）</t>
   </si>
   <si>
     <t>棋子预制体资源ID（阶级数组，暂时三阶相同）</t>
@@ -242,6 +242,9 @@
     <t>1</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
     <t>2301,2301,2301</t>
   </si>
   <si>
@@ -251,295 +254,286 @@
     <t>13001,13001,13001</t>
   </si>
   <si>
+    <t>52000,832,1248</t>
+  </si>
+  <si>
+    <t>100,160,240</t>
+  </si>
+  <si>
+    <t>60,60,60</t>
+  </si>
+  <si>
+    <t>22,35,53</t>
+  </si>
+  <si>
+    <t>0.7,1.0,1.4</t>
+  </si>
+  <si>
+    <t>10,11,12</t>
+  </si>
+  <si>
+    <t>18,29,43</t>
+  </si>
+  <si>
+    <t>0.15,0.2,0.25</t>
+  </si>
+  <si>
+    <t>1.5,1.7,2.0</t>
+  </si>
+  <si>
+    <t>0,0,0</t>
+  </si>
+  <si>
+    <t>11,11,11</t>
+  </si>
+  <si>
+    <t>12,12,12</t>
+  </si>
+  <si>
+    <t>13,13,13</t>
+  </si>
+  <si>
+    <t>14,14,14</t>
+  </si>
+  <si>
+    <t>暂无,暂无,暂无</t>
+  </si>
+  <si>
+    <t>嫦娥</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>2304,2304,2304</t>
+  </si>
+  <si>
+    <t>1304,1304,1304</t>
+  </si>
+  <si>
+    <t>13004,13004,13004</t>
+  </si>
+  <si>
     <t>400,640,960</t>
   </si>
   <si>
-    <t>100,160,240</t>
-  </si>
-  <si>
-    <t>60,60,60</t>
+    <t>180,288,432</t>
+  </si>
+  <si>
+    <t>0.6,0.8,1</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>15,24,36</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>38,61,97</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>2310,2310,2310</t>
+  </si>
+  <si>
+    <t>1310,1310,1310</t>
+  </si>
+  <si>
+    <t>13010,13010,13010</t>
+  </si>
+  <si>
+    <t>60000,957,1435</t>
+  </si>
+  <si>
+    <t>160,256,384</t>
+  </si>
+  <si>
+    <t>1,1.6,2.4</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
   </si>
   <si>
     <t>10,16,24</t>
   </si>
   <si>
-    <t>0.5,0.8,1.2</t>
-  </si>
-  <si>
-    <t>10,11,12</t>
-  </si>
-  <si>
-    <t>18,29,43</t>
-  </si>
-  <si>
-    <t>13,21,31</t>
-  </si>
-  <si>
-    <t>0.15,0.2,0.25</t>
-  </si>
-  <si>
-    <t>1.5,1.7,2.0</t>
-  </si>
-  <si>
-    <t>0,0,0</t>
-  </si>
-  <si>
-    <t>11,11,11</t>
-  </si>
-  <si>
-    <t>12,12,12</t>
-  </si>
-  <si>
-    <t>13,13,13</t>
-  </si>
-  <si>
-    <t>14,14,14</t>
-  </si>
-  <si>
-    <t>暂无,暂无,暂无</t>
-  </si>
-  <si>
-    <t>嫦娥</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>2304,2304,2304</t>
-  </si>
-  <si>
-    <t>1304,1304,1304</t>
-  </si>
-  <si>
-    <t>13004,13004,13004</t>
-  </si>
-  <si>
-    <t>330,528,792</t>
-  </si>
-  <si>
-    <t>180,288,432</t>
+    <t>6,10,14</t>
+  </si>
+  <si>
+    <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>42,67,101</t>
+  </si>
+  <si>
+    <t>31,31,31</t>
+  </si>
+  <si>
+    <t>32,32,32</t>
+  </si>
+  <si>
+    <t>33,33,33</t>
+  </si>
+  <si>
+    <t>34,34,34</t>
+  </si>
+  <si>
+    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>恶魂</t>
+  </si>
+  <si>
+    <t>2311,2311,2311</t>
+  </si>
+  <si>
+    <t>1311,1311,1311</t>
+  </si>
+  <si>
+    <t>13011,13011,13011</t>
+  </si>
+  <si>
+    <t>240,384,576</t>
+  </si>
+  <si>
+    <t>0.8,1.28,1.92</t>
+  </si>
+  <si>
+    <t>16,26,38</t>
+  </si>
+  <si>
+    <t>44,70,106</t>
+  </si>
+  <si>
+    <t>41,41,41</t>
+  </si>
+  <si>
+    <t>42,42,42</t>
+  </si>
+  <si>
+    <t>43,43,43</t>
+  </si>
+  <si>
+    <t>44,44,44</t>
+  </si>
+  <si>
+    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗杨戬</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>2312,2312,2312</t>
+  </si>
+  <si>
+    <t>13012,13012,13012</t>
+  </si>
+  <si>
+    <t>1008,1613,2419</t>
+  </si>
+  <si>
+    <t>72,115,172</t>
   </si>
   <si>
     <t>80,80,80</t>
   </si>
   <si>
-    <t>0.8,0.8,0.8</t>
-  </si>
-  <si>
-    <t>8,9,10</t>
-  </si>
-  <si>
-    <t>15,24,36</t>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-  </si>
-  <si>
-    <t>1.5,1.5,1.5</t>
-  </si>
-  <si>
-    <t>50,80,120</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>22,22,22</t>
-  </si>
-  <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>24,24,24</t>
-  </si>
-  <si>
-    <t>敌人测试</t>
-  </si>
-  <si>
-    <t>2309,2309,2309</t>
-  </si>
-  <si>
-    <t>400,400,400</t>
+    <t>20,32,48</t>
+  </si>
+  <si>
+    <t>0.6,0.96,1.44</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>60,96,144</t>
+  </si>
+  <si>
+    <t>36,58,86</t>
+  </si>
+  <si>
+    <t>0.2,0.25,0.3</t>
+  </si>
+  <si>
+    <t>2.0,2.2,2.5</t>
+  </si>
+  <si>
+    <t>51,51,51</t>
+  </si>
+  <si>
+    <t>52,52,52</t>
+  </si>
+  <si>
+    <t>53,53,53</t>
+  </si>
+  <si>
+    <t>55,55,55</t>
+  </si>
+  <si>
+    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
+  </si>
+  <si>
+    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>黑暗哮天犬</t>
+  </si>
+  <si>
+    <t>2313,2313,2313</t>
+  </si>
+  <si>
+    <t>13013,13013,13013</t>
+  </si>
+  <si>
+    <t>56,56,56</t>
+  </si>
+  <si>
+    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
+  </si>
+  <si>
+    <t>稻草人</t>
+  </si>
+  <si>
+    <t>2399,2399,2399</t>
+  </si>
+  <si>
+    <t>1399,1399,1399</t>
+  </si>
+  <si>
+    <t>13999,13999,13999</t>
+  </si>
+  <si>
+    <t>2000,2000,2000</t>
   </si>
   <si>
     <t>100,100,100</t>
-  </si>
-  <si>
-    <t>10,10,10</t>
-  </si>
-  <si>
-    <t>0.5,0.5,0.5</t>
-  </si>
-  <si>
-    <t>10,20,20</t>
-  </si>
-  <si>
-    <t>20,20,20</t>
-  </si>
-  <si>
-    <t>邪灵</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>2310,2310,2310</t>
-  </si>
-  <si>
-    <t>1310,1310,1310</t>
-  </si>
-  <si>
-    <t>13010,13010,13010</t>
-  </si>
-  <si>
-    <t>240,384,576</t>
-  </si>
-  <si>
-    <t>160,256,384</t>
-  </si>
-  <si>
-    <t>0.8,1.28,1.92</t>
-  </si>
-  <si>
-    <t>2,2,2</t>
-  </si>
-  <si>
-    <t>6,10,14</t>
-  </si>
-  <si>
-    <t>0.05,0.05,0.05</t>
-  </si>
-  <si>
-    <t>60,96,144</t>
-  </si>
-  <si>
-    <t>31,31,31</t>
-  </si>
-  <si>
-    <t>32,32,32</t>
-  </si>
-  <si>
-    <t>33,33,33</t>
-  </si>
-  <si>
-    <t>34,34,34</t>
-  </si>
-  <si>
-    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>恶魂</t>
-  </si>
-  <si>
-    <t>2311,2311,2311</t>
-  </si>
-  <si>
-    <t>1311,1311,1311</t>
-  </si>
-  <si>
-    <t>13011,13011,13011</t>
-  </si>
-  <si>
-    <t>16,26,38</t>
-  </si>
-  <si>
-    <t>44,70,106</t>
-  </si>
-  <si>
-    <t>41,41,41</t>
-  </si>
-  <si>
-    <t>42,42,42</t>
-  </si>
-  <si>
-    <t>43,43,43</t>
-  </si>
-  <si>
-    <t>44,44,44</t>
-  </si>
-  <si>
-    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗杨戬</t>
-  </si>
-  <si>
-    <t>2312,2312,2312</t>
-  </si>
-  <si>
-    <t>13012,13012,13012</t>
-  </si>
-  <si>
-    <t>1008,1613,2419</t>
-  </si>
-  <si>
-    <t>72,115,172</t>
-  </si>
-  <si>
-    <t>20,32,48</t>
-  </si>
-  <si>
-    <t>0.6,0.96,1.44</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>36,58,86</t>
-  </si>
-  <si>
-    <t>0.2,0.25,0.3</t>
-  </si>
-  <si>
-    <t>2.0,2.2,2.5</t>
-  </si>
-  <si>
-    <t>51,51,51</t>
-  </si>
-  <si>
-    <t>52,52,52</t>
-  </si>
-  <si>
-    <t>53,53,53</t>
-  </si>
-  <si>
-    <t>55,55,55</t>
-  </si>
-  <si>
-    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
-  </si>
-  <si>
-    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗哮天犬</t>
-  </si>
-  <si>
-    <t>2313,2313,2313</t>
-  </si>
-  <si>
-    <t>13013,13013,13013</t>
-  </si>
-  <si>
-    <t>56,56,56</t>
-  </si>
-  <si>
-    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>稻草人</t>
-  </si>
-  <si>
-    <t>2399,2399,2399</t>
-  </si>
-  <si>
-    <t>1399,1399,1399</t>
-  </si>
-  <si>
-    <t>13999,13999,13999</t>
-  </si>
-  <si>
-    <t>2000,2000,2000</t>
   </si>
   <si>
     <t>1,1,1</t>
@@ -1547,7 +1541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1556,8 +1550,7 @@
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="37" customWidth="1"/>
-    <col min="8" max="8" width="35" customWidth="1"/>
+    <col min="7" max="8" width="37" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
     <col min="10" max="11" width="42" customWidth="1"/>
     <col min="12" max="13" width="36" customWidth="1"/>
@@ -1925,37 +1918,37 @@
         <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>81</v>
@@ -2035,34 +2028,34 @@
         <v>96</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>84</v>
       </c>
       <c r="P6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="S6" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="T6" s="1">
         <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -2071,16 +2064,16 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA6" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AA6" s="2" t="s">
+      <c r="AB6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="AD6" s="1">
         <v>2</v>
@@ -2093,68 +2086,66 @@
     <row r="7" ht="15" customHeight="1" spans="1:32">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>109</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="T7" s="1">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="W7" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2163,33 +2154,33 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="AD7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2199,52 +2190,52 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>84</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2253,88 +2244,88 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AD8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8" s="1"/>
       <c r="AF8" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:32">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T9" s="1">
+        <v>2</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="T9" s="1">
-        <v>3.5</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -2343,85 +2334,87 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="AD9" s="1">
-        <v>2</v>
-      </c>
-      <c r="AE9" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="AF9" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:32">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>152</v>
+        <v>84</v>
       </c>
       <c r="T10" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>84</v>
@@ -2433,35 +2426,33 @@
         <v>0</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="AD10" s="1">
         <v>1</v>
       </c>
-      <c r="AE10" s="1" t="s">
-        <v>159</v>
-      </c>
+      <c r="AE10" s="1"/>
       <c r="AF10" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:32">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
-        <v>13</v>
+        <v>9999</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2470,23 +2461,21 @@
         <v>0</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>70</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>84</v>
@@ -2495,10 +2484,10 @@
         <v>84</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>84</v>
@@ -2507,13 +2496,13 @@
         <v>84</v>
       </c>
       <c r="T11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>84</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>84</v>
@@ -2524,37 +2513,35 @@
       <c r="Y11" s="1">
         <v>0</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="Z11" s="2"/>
       <c r="AA11" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AD11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="2" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:32">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
-        <v>9999</v>
+        <v>1001</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E12" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2562,49 +2549,49 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="N12" s="2" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -2614,105 +2601,19 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AD12" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="1:32">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="X13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="AD13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="2" t="s">
         <v>89</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -254,7 +254,7 @@
     <t>13001,13001,13001</t>
   </si>
   <si>
-    <t>52000,832,1248</t>
+    <t>520,832,1248</t>
   </si>
   <si>
     <t>100,160,240</t>
@@ -365,7 +365,7 @@
     <t>13010,13010,13010</t>
   </si>
   <si>
-    <t>60000,957,1435</t>
+    <t>600,957,1435</t>
   </si>
   <si>
     <t>160,256,384</t>
@@ -579,14 +579,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1042,148 +1035,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1542,7 +1535,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="184">
   <si>
     <t>#</t>
   </si>
@@ -116,13 +116,16 @@
     <t>Skill2Id</t>
   </si>
   <si>
+    <t>UltimateId</t>
+  </si>
+  <si>
     <t>AIType</t>
   </si>
   <si>
     <t>CustomData</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>StoryText</t>
   </si>
   <si>
     <t>int</t>
@@ -224,6 +227,9 @@
     <t>技能一ID（三个值，暂时相同）</t>
   </si>
   <si>
+    <t>技能二ID（三个值，暂时相同）（没有则不填）</t>
+  </si>
+  <si>
     <t>大招ID（三个值，暂时相同）</t>
   </si>
   <si>
@@ -233,7 +239,7 @@
     <t>自定义数据（JSON格式）</t>
   </si>
   <si>
-    <t>棋子的背景描述（三个值：一阶/二阶/三阶）</t>
+    <t>棋子背景故事（多段，100-200字每段）</t>
   </si>
   <si>
     <t>后羿</t>
@@ -296,250 +302,256 @@
     <t>14,14,14</t>
   </si>
   <si>
+    <t>后羿是上古射神，以九日射术闻名于世。他用古老的弓箭守护着天下苍生，每一箭都蕴含着太阳般炽热的力量。在人间失望后，他独自踏上寻找光明的旅程。,经历了无数次失败和挫折，后羿逐渐放弃了对人类的期待，但那份护世的心念从未消散。他的箭术已臻至化境，每一次射击都能改变战局的走向。,最终，后羿终于明白了真谛——光明不是来自太阳，而是来自心中的坚守。他重拾信心，以更强大的姿态归来，誓要守护最后的希望。</t>
+  </si>
+  <si>
+    <t>嫦娥</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>2304,2304,2304</t>
+  </si>
+  <si>
+    <t>1304,1304,1304</t>
+  </si>
+  <si>
+    <t>13004,13004,13004</t>
+  </si>
+  <si>
+    <t>400,640,960</t>
+  </si>
+  <si>
+    <t>180,288,432</t>
+  </si>
+  <si>
+    <t>0.6,0.8,1</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>15,24,36</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>38,61,97</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>月宫仙子嫦娥，以其冰冷的法术和神秘的魔力著称。她曾为了守护众生而独自飞往月宫，在漫长的岁月中，她的心如同月光般清冷，但对世界的关怀从未改变。,在无尽的孤寂中，嫦娥逐渐领悟到了冰的真谛——坚硬如冰，却能映照世间一切。她的魔法变得更加强大，但同时也更加冷漠。她开始思考，为何一个人要承受如此沉重的负担。,月光下，嫦娥终于做出了决定。她放弃了永恒的孤寂，决心与同伴共同对抗黑暗。月华在她周身舞动，化作守护的力量，闪耀出温暖的光芒。</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>2310,2310,2310</t>
+  </si>
+  <si>
+    <t>1310,1310,1310</t>
+  </si>
+  <si>
+    <t>13010,13010,13010</t>
+  </si>
+  <si>
+    <t>600,957,1435</t>
+  </si>
+  <si>
+    <t>160,256,384</t>
+  </si>
+  <si>
+    <t>1,1.6,2.4</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>10,16,24</t>
+  </si>
+  <si>
+    <t>6,10,14</t>
+  </si>
+  <si>
+    <t>0.05,0.05,0.05</t>
+  </si>
+  <si>
+    <t>42,67,101</t>
+  </si>
+  <si>
+    <t>31,31,31</t>
+  </si>
+  <si>
+    <t>32,32,32</t>
+  </si>
+  <si>
+    <t>33,33,33</t>
+  </si>
+  <si>
+    <t>34,34,34</t>
+  </si>
+  <si>
+    <t>这曾是天界最纯洁的仙灵，拥有无与伦比的美丽和力量。然而，一次意外让它接触到了黑暗的力量，那股腐蚀性的能量渐渐侵蚀了它的灵魂，原本的善良逐步被扭曲和怨念所吞噬。,邪灵已经彻底被黑暗污染，原有的记忆和品性荡然无存。它成为了黑暗的信徒，用腐蚀和痛苦去传播黑暗。每一次出击，都留下永久的伤痕。它不再记得自己曾经是谁。,邪灵已经进化成了黑暗的化身，它体内的黑暗力量达到了巅峰。它的存在本身就是对光明的诅咒，没有任何东西能拯救它，它只会继续传播黑暗和绝望。</t>
+  </si>
+  <si>
+    <t>恶魂</t>
+  </si>
+  <si>
+    <t>2311,2311,2311</t>
+  </si>
+  <si>
+    <t>1311,1311,1311</t>
+  </si>
+  <si>
+    <t>13011,13011,13011</t>
+  </si>
+  <si>
+    <t>240,384,576</t>
+  </si>
+  <si>
+    <t>0.8,1.28,1.92</t>
+  </si>
+  <si>
+    <t>16,26,38</t>
+  </si>
+  <si>
+    <t>44,70,106</t>
+  </si>
+  <si>
+    <t>41,41,41</t>
+  </si>
+  <si>
+    <t>42,42,42</t>
+  </si>
+  <si>
+    <t>43,43,43</t>
+  </si>
+  <si>
+    <t>44,44,44</t>
+  </si>
+  <si>
+    <t>恶魂是世间所有邪恶与负面能量的聚合体，它没有固定的形态，只是一团扭曲的黑暗。它在人性的恐惧和绝望中诞生，随处可见的罪恶为它不断补充力量。,恶魂已经成长为足以威胁一方的存在。它会化作人们心中的梦魇，引发更多的杀戮和痛苦。它的力量来自于每一个选择了黑暗的灵魂。,恶魂已经演化到了巅峰形态，成为了黑暗本身的化身。它不再是单纯的能量集合，而是拥有了自己的意志和野心，渴望吞噬整个世界的光明。</t>
+  </si>
+  <si>
+    <t>黑暗杨戬</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>2312,2312,2312</t>
+  </si>
+  <si>
+    <t>13012,13012,13012</t>
+  </si>
+  <si>
+    <t>1008,1613,2419</t>
+  </si>
+  <si>
+    <t>72,115,172</t>
+  </si>
+  <si>
+    <t>80,80,80</t>
+  </si>
+  <si>
+    <t>20,32,48</t>
+  </si>
+  <si>
+    <t>0.6,0.96,1.44</t>
+  </si>
+  <si>
+    <t>3,4,5</t>
+  </si>
+  <si>
+    <t>60,96,144</t>
+  </si>
+  <si>
+    <t>36,58,86</t>
+  </si>
+  <si>
+    <t>0.2,0.25,0.3</t>
+  </si>
+  <si>
+    <t>2.0,2.2,2.5</t>
+  </si>
+  <si>
+    <t>51,51,51</t>
+  </si>
+  <si>
+    <t>52,52,52</t>
+  </si>
+  <si>
+    <t>53,53,53</t>
+  </si>
+  <si>
+    <t>55,55,55</t>
+  </si>
+  <si>
+    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0,"Skill2Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
+  </si>
+  <si>
+    <t>杨戬曾是天界的神将，正义与力量的象征。但一次任务中，他被黑暗力量击中，虽然活了下来，但那股邪恶的能量开始侵蚀他的灵魂。他痛苦地与黑暗对抗，但最终还是逐渐沦陷。,黑暗完全控制了杨戬。他失去了自我，成为了黑暗的傀儡。他挥舞着曾经守护天界的神兵，却用来摧毁一切美好。他的力量被黑暗扭曲，变得更加恐怖。,黑暗杨戬已经完全进化，成为了黑暗势力的最强战士。他不再是曾经的神将，而是黑暗的化身。他召唤出了黑暗的仆从——哮天犬，一同在黑暗中肆虐。</t>
+  </si>
+  <si>
+    <t>黑暗哮天犬</t>
+  </si>
+  <si>
+    <t>2313,2313,2313</t>
+  </si>
+  <si>
+    <t>13013,13013,13013</t>
+  </si>
+  <si>
+    <t>56,56,56</t>
+  </si>
+  <si>
+    <t>哮天犬是杨戬最忠诚的伙伴，曾与他一同守护天界。然而，当杨戬被黑暗侵蚀时，哮天犬也未能幸免。它感受到了主人的痛苦和堕落，却无力阻止。,黑暗哮天犬已经完全被邪恶所控制。它失去了原有的忠诚和温顺，化作了黑暗的猎犬。它会毫不犹豫地为主人撕碎任何敌人，无论对手是谁。,黑暗哮天犬已经演化成了黑暗的完美战兽，拥有难以抵挡的力量。它与黑暗杨戬一同出现，为黑暗势力扫平一切障碍。</t>
+  </si>
+  <si>
+    <t>稻草人</t>
+  </si>
+  <si>
+    <t>2399,2399,2399</t>
+  </si>
+  <si>
+    <t>1399,1399,1399</t>
+  </si>
+  <si>
+    <t>13999,13999,13999</t>
+  </si>
+  <si>
+    <t>2000,2000,2000</t>
+  </si>
+  <si>
+    <t>100,100,100</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>暂无,暂无,暂无</t>
-  </si>
-  <si>
-    <t>嫦娥</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>2304,2304,2304</t>
-  </si>
-  <si>
-    <t>1304,1304,1304</t>
-  </si>
-  <si>
-    <t>13004,13004,13004</t>
-  </si>
-  <si>
-    <t>400,640,960</t>
-  </si>
-  <si>
-    <t>180,288,432</t>
-  </si>
-  <si>
-    <t>0.6,0.8,1</t>
-  </si>
-  <si>
-    <t>8,9,10</t>
-  </si>
-  <si>
-    <t>15,24,36</t>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-  </si>
-  <si>
-    <t>1.5,1.5,1.5</t>
-  </si>
-  <si>
-    <t>38,61,97</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>22,22,22</t>
-  </si>
-  <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>24,24,24</t>
-  </si>
-  <si>
-    <t>邪灵</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>2310,2310,2310</t>
-  </si>
-  <si>
-    <t>1310,1310,1310</t>
-  </si>
-  <si>
-    <t>13010,13010,13010</t>
-  </si>
-  <si>
-    <t>600,957,1435</t>
-  </si>
-  <si>
-    <t>160,256,384</t>
-  </si>
-  <si>
-    <t>1,1.6,2.4</t>
-  </si>
-  <si>
-    <t>2,2,2</t>
-  </si>
-  <si>
-    <t>10,16,24</t>
-  </si>
-  <si>
-    <t>6,10,14</t>
-  </si>
-  <si>
-    <t>0.05,0.05,0.05</t>
-  </si>
-  <si>
-    <t>42,67,101</t>
-  </si>
-  <si>
-    <t>31,31,31</t>
-  </si>
-  <si>
-    <t>32,32,32</t>
-  </si>
-  <si>
-    <t>33,33,33</t>
-  </si>
-  <si>
-    <t>34,34,34</t>
-  </si>
-  <si>
-    <t>曾经纯洁的仙灵，被黑暗力量污染后失去自我。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>恶魂</t>
-  </si>
-  <si>
-    <t>2311,2311,2311</t>
-  </si>
-  <si>
-    <t>1311,1311,1311</t>
-  </si>
-  <si>
-    <t>13011,13011,13011</t>
-  </si>
-  <si>
-    <t>240,384,576</t>
-  </si>
-  <si>
-    <t>0.8,1.28,1.92</t>
-  </si>
-  <si>
-    <t>16,26,38</t>
-  </si>
-  <si>
-    <t>44,70,106</t>
-  </si>
-  <si>
-    <t>41,41,41</t>
-  </si>
-  <si>
-    <t>42,42,42</t>
-  </si>
-  <si>
-    <t>43,43,43</t>
-  </si>
-  <si>
-    <t>44,44,44</t>
-  </si>
-  <si>
-    <t>世间邪恶与负能量的集合体，无实体。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗杨戬</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>2312,2312,2312</t>
-  </si>
-  <si>
-    <t>13012,13012,13012</t>
-  </si>
-  <si>
-    <t>1008,1613,2419</t>
-  </si>
-  <si>
-    <t>72,115,172</t>
-  </si>
-  <si>
-    <t>80,80,80</t>
-  </si>
-  <si>
-    <t>20,32,48</t>
-  </si>
-  <si>
-    <t>0.6,0.96,1.44</t>
-  </si>
-  <si>
-    <t>3,4,5</t>
-  </si>
-  <si>
-    <t>60,96,144</t>
-  </si>
-  <si>
-    <t>36,58,86</t>
-  </si>
-  <si>
-    <t>0.2,0.25,0.3</t>
-  </si>
-  <si>
-    <t>2.0,2.2,2.5</t>
-  </si>
-  <si>
-    <t>51,51,51</t>
-  </si>
-  <si>
-    <t>52,52,52</t>
-  </si>
-  <si>
-    <t>53,53,53</t>
-  </si>
-  <si>
-    <t>55,55,55</t>
-  </si>
-  <si>
-    <t>{"Phases":[{"PhaseNum":1,"HealthPercentThreshold":60,"BuffIds":[],"SkillOverride":null,"UltimateModifier":null,"SubordinateSpawn":null},{"PhaseNum":2,"HealthPercentThreshold":30,"BuffIds":[22],"SkillOverride":{"Skill2Id":54},"UltimateModifier":null,"SubordinateSpawn":{"ChessId":13,"Quantity":1,"InheritRatio":0.8}},{"PhaseNum":3,"HealthPercentThreshold":0,"BuffIds":[24,25],"SkillOverride":{"NormalAttackSkillId":53,"Skill1Id":0},"UltimateModifier":null,"SubordinateSpawn":null}]}</t>
-  </si>
-  <si>
-    <t>杨戬被黑暗力量侵蚀后的形态。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>黑暗哮天犬</t>
-  </si>
-  <si>
-    <t>2313,2313,2313</t>
-  </si>
-  <si>
-    <t>13013,13013,13013</t>
-  </si>
-  <si>
-    <t>56,56,56</t>
-  </si>
-  <si>
-    <t>黑暗杨戬的从属单位。,暂无,暂无</t>
-  </si>
-  <si>
-    <t>稻草人</t>
-  </si>
-  <si>
-    <t>2399,2399,2399</t>
-  </si>
-  <si>
-    <t>1399,1399,1399</t>
-  </si>
-  <si>
-    <t>13999,13999,13999</t>
-  </si>
-  <si>
-    <t>2000,2000,2000</t>
-  </si>
-  <si>
-    <t>100,100,100</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>召唤师-狂战士</t>
@@ -579,7 +591,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1035,148 +1054,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1534,8 +1553,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AG12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1559,12 +1578,13 @@
     <col min="25" max="25" width="16" customWidth="1"/>
     <col min="26" max="27" width="36" customWidth="1"/>
     <col min="28" max="28" width="30" customWidth="1"/>
-    <col min="29" max="29" width="28" customWidth="1"/>
-    <col min="30" max="30" width="41" customWidth="1"/>
-    <col min="31" max="32" width="50" customWidth="1"/>
+    <col min="29" max="29" width="44" customWidth="1"/>
+    <col min="30" max="30" width="28" customWidth="1"/>
+    <col min="31" max="31" width="41" customWidth="1"/>
+    <col min="32" max="33" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,11 +1618,12 @@
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
-      <c r="AD1" s="1"/>
+      <c r="AD1" s="2"/>
       <c r="AE1" s="1"/>
-      <c r="AF1" s="2"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="2"/>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1688,218 +1709,227 @@
       <c r="AC2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="AG2" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:32">
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AF3" s="2" t="s">
-        <v>37</v>
+      <c r="AF3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD4" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="AD4" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="AE4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF4" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="AF4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:32">
+    <row r="5" ht="15" customHeight="1" spans="1:33">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -1908,55 +1938,55 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T5" s="1">
         <v>3</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X5" s="1">
         <v>0</v>
@@ -1965,33 +1995,34 @@
         <v>0</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD5" s="1">
+        <v>89</v>
+      </c>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE5" s="1">
         <v>2</v>
       </c>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="2" t="s">
-        <v>89</v>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:32">
+    <row r="6" ht="15" customHeight="1" spans="1:33">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -2000,55 +2031,55 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T6" s="1">
         <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -2057,33 +2088,34 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD6" s="1">
+        <v>107</v>
+      </c>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE6" s="1">
         <v>2</v>
       </c>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="2" t="s">
-        <v>89</v>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:32">
+    <row r="7" ht="15" customHeight="1" spans="1:33">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2093,52 +2125,52 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="T7" s="1">
         <v>3.5</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2147,33 +2179,34 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD7" s="1">
+        <v>125</v>
+      </c>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE7" s="1">
         <v>1</v>
       </c>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="2" t="s">
-        <v>124</v>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:32">
+    <row r="8" ht="15" customHeight="1" spans="1:33">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>11</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2183,52 +2216,52 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2237,33 +2270,34 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD8" s="1">
+        <v>138</v>
+      </c>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE8" s="1">
         <v>2</v>
       </c>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="2" t="s">
-        <v>137</v>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:32">
+    <row r="9" ht="15" customHeight="1" spans="1:33">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>12</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2273,52 +2307,52 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="T9" s="1">
         <v>2</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
@@ -2327,35 +2361,36 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD9" s="1">
+        <v>157</v>
+      </c>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AE9" s="1">
         <v>1</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>157</v>
+      <c r="AF9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:32">
+    <row r="10" ht="15" customHeight="1" spans="1:33">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>13</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2365,52 +2400,52 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T10" s="1">
         <v>4</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
@@ -2419,33 +2454,34 @@
         <v>0</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD10" s="1">
+        <v>86</v>
+      </c>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE10" s="1">
         <v>1</v>
       </c>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="2" t="s">
-        <v>162</v>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:32">
+    <row r="11" ht="15" customHeight="1" spans="1:33">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>9999</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2456,49 +2492,49 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T11" s="1">
         <v>0</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
@@ -2508,30 +2544,31 @@
       </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD11" s="1">
+        <v>173</v>
+      </c>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE11" s="1">
         <v>3</v>
       </c>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="2" t="s">
-        <v>89</v>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:32">
+    <row r="12" ht="15" customHeight="1" spans="1:33">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1001</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2542,49 +2579,49 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="O12" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -2594,20 +2631,21 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AD12" s="1">
+        <v>173</v>
+      </c>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="2" t="s">
-        <v>89</v>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -308,63 +308,66 @@
     <t>嫦娥</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>2304,2304,2304</t>
+  </si>
+  <si>
+    <t>1304,1304,1304</t>
+  </si>
+  <si>
+    <t>13004,13004,13004</t>
+  </si>
+  <si>
+    <t>400,640,960</t>
+  </si>
+  <si>
+    <t>180,288,432</t>
+  </si>
+  <si>
+    <t>0.6,0.8,1</t>
+  </si>
+  <si>
+    <t>8,9,10</t>
+  </si>
+  <si>
+    <t>15,24,36</t>
+  </si>
+  <si>
+    <t>0.15,0.15,0.15</t>
+  </si>
+  <si>
+    <t>1.5,1.5,1.5</t>
+  </si>
+  <si>
+    <t>38,61,97</t>
+  </si>
+  <si>
+    <t>21,21,21</t>
+  </si>
+  <si>
+    <t>22,22,22</t>
+  </si>
+  <si>
+    <t>23,23,23</t>
+  </si>
+  <si>
+    <t>24,24,24</t>
+  </si>
+  <si>
+    <t>月宫仙子嫦娥，以其冰冷的法术和神秘的魔力著称。她曾为了守护众生而独自飞往月宫，在漫长的岁月中，她的心如同月光般清冷，但对世界的关怀从未改变。,在无尽的孤寂中，嫦娥逐渐领悟到了冰的真谛——坚硬如冰，却能映照世间一切。她的魔法变得更加强大，但同时也更加冷漠。她开始思考，为何一个人要承受如此沉重的负担。,月光下，嫦娥终于做出了决定。她放弃了永恒的孤寂，决心与同伴共同对抗黑暗。月华在她周身舞动，化作守护的力量，闪耀出温暖的光芒。</t>
+  </si>
+  <si>
+    <t>邪灵</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>2304,2304,2304</t>
-  </si>
-  <si>
-    <t>1304,1304,1304</t>
-  </si>
-  <si>
-    <t>13004,13004,13004</t>
-  </si>
-  <si>
-    <t>400,640,960</t>
-  </si>
-  <si>
-    <t>180,288,432</t>
-  </si>
-  <si>
-    <t>0.6,0.8,1</t>
-  </si>
-  <si>
-    <t>8,9,10</t>
-  </si>
-  <si>
-    <t>15,24,36</t>
-  </si>
-  <si>
-    <t>0.15,0.15,0.15</t>
-  </si>
-  <si>
-    <t>1.5,1.5,1.5</t>
-  </si>
-  <si>
-    <t>38,61,97</t>
-  </si>
-  <si>
-    <t>21,21,21</t>
-  </si>
-  <si>
-    <t>22,22,22</t>
-  </si>
-  <si>
-    <t>23,23,23</t>
-  </si>
-  <si>
-    <t>24,24,24</t>
-  </si>
-  <si>
-    <t>月宫仙子嫦娥，以其冰冷的法术和神秘的魔力著称。她曾为了守护众生而独自飞往月宫，在漫长的岁月中，她的心如同月光般清冷，但对世界的关怀从未改变。,在无尽的孤寂中，嫦娥逐渐领悟到了冰的真谛——坚硬如冰，却能映照世间一切。她的魔法变得更加强大，但同时也更加冷漠。她开始思考，为何一个人要承受如此沉重的负担。,月光下，嫦娥终于做出了决定。她放弃了永恒的孤寂，决心与同伴共同对抗黑暗。月华在她周身舞动，化作守护的力量，闪耀出温暖的光芒。</t>
-  </si>
-  <si>
-    <t>邪灵</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>2310,2310,2310</t>
   </si>
   <si>
@@ -416,6 +419,9 @@
     <t>恶魂</t>
   </si>
   <si>
+    <t>2,3</t>
+  </si>
+  <si>
     <t>2311,2311,2311</t>
   </si>
   <si>
@@ -453,9 +459,6 @@
   </si>
   <si>
     <t>黑暗杨戬</t>
-  </si>
-  <si>
-    <t>104</t>
   </si>
   <si>
     <t>2312,2312,2312</t>
@@ -2123,24 +2126,26 @@
       <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>79</v>
@@ -2149,28 +2154,28 @@
         <v>86</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T7" s="1">
         <v>3.5</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>103</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2179,24 +2184,24 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AE7" s="1">
         <v>1</v>
       </c>
       <c r="AF7" s="1"/>
       <c r="AG7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:33">
@@ -2206,7 +2211,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2214,24 +2219,26 @@
       <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>79</v>
@@ -2240,28 +2247,28 @@
         <v>86</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="V8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2270,24 +2277,24 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AE8" s="1">
         <v>2</v>
       </c>
       <c r="AF8" s="1"/>
       <c r="AG8" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:33">
@@ -2297,7 +2304,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2305,51 +2312,53 @@
       <c r="F9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T9" s="1">
         <v>2</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>86</v>
@@ -2361,26 +2370,26 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AE9" s="1">
         <v>1</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:33">
@@ -2390,7 +2399,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2399,17 +2408,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>72</v>
-      </c>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>86</v>
@@ -2457,7 +2464,7 @@
         <v>86</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>86</v>
@@ -2471,7 +2478,7 @@
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:33">
@@ -2481,7 +2488,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2492,19 +2499,19 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>86</v>
@@ -2513,10 +2520,10 @@
         <v>86</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>86</v>
@@ -2544,21 +2551,21 @@
       </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AE11" s="1">
         <v>3</v>
       </c>
       <c r="AF11" s="1"/>
       <c r="AG11" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:33">
@@ -2568,7 +2575,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2579,49 +2586,49 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>72</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -2631,21 +2638,21 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AE12" s="1">
         <v>0</v>
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="183">
   <si>
     <t>#</t>
   </si>
@@ -518,6 +518,9 @@
     <t>黑暗哮天犬</t>
   </si>
   <si>
+    <t>-1</t>
+  </si>
+  <si>
     <t>2313,2313,2313</t>
   </si>
   <si>
@@ -551,37 +554,28 @@
     <t>1,1,1</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>暂无,暂无,暂无</t>
   </si>
   <si>
     <t>召唤师-狂战士</t>
   </si>
   <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>1105</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>1.5</t>
+    <t>2101,2101,2101</t>
+  </si>
+  <si>
+    <t>1105,1105,1105</t>
+  </si>
+  <si>
+    <t>10,10,10</t>
+  </si>
+  <si>
+    <t>0.5,0.5,0.5</t>
+  </si>
+  <si>
+    <t>6,6,6</t>
+  </si>
+  <si>
+    <t>20,20,20</t>
   </si>
 </sst>
 </file>
@@ -594,14 +588,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1057,148 +1044,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1557,7 +1544,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2407,16 +2394,20 @@
       <c r="F10" s="1">
         <v>0</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>86</v>
@@ -2464,7 +2455,7 @@
         <v>86</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>86</v>
@@ -2478,7 +2469,7 @@
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:33">
@@ -2488,7 +2479,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2496,22 +2487,26 @@
       <c r="F11" s="1">
         <v>0</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I11" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>86</v>
@@ -2520,10 +2515,10 @@
         <v>86</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>86</v>
@@ -2549,16 +2544,18 @@
       <c r="Y11" s="1">
         <v>0</v>
       </c>
-      <c r="Z11" s="2"/>
+      <c r="Z11" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="AA11" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AE11" s="1">
         <v>3</v>
@@ -2583,8 +2580,12 @@
       <c r="F12" s="1">
         <v>0</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>177</v>
       </c>
@@ -2595,13 +2596,13 @@
         <v>178</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>179</v>
@@ -2622,13 +2623,13 @@
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
@@ -2636,16 +2637,18 @@
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="2"/>
+      <c r="Z12" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="AA12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="AE12" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1544,7 +1544,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="182">
   <si>
     <t>#</t>
   </si>
@@ -471,9 +471,6 @@
   </si>
   <si>
     <t>72,115,172</t>
-  </si>
-  <si>
-    <t>80,80,80</t>
   </si>
   <si>
     <t>20,32,48</t>
@@ -1544,7 +1541,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2321,31 +2318,31 @@
         <v>147</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="T9" s="1">
         <v>2</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>86</v>
@@ -2357,26 +2354,26 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA9" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AE9" s="1">
         <v>1</v>
       </c>
       <c r="AF9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AG9" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:33">
@@ -2386,7 +2383,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2395,19 +2392,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>86</v>
@@ -2455,7 +2452,7 @@
         <v>86</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>86</v>
@@ -2469,7 +2466,7 @@
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:33">
@@ -2479,7 +2476,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2488,37 +2485,37 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="Q11" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>86</v>
@@ -2562,7 +2559,7 @@
       </c>
       <c r="AF11" s="1"/>
       <c r="AG11" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:33">
@@ -2572,7 +2569,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2581,43 +2578,43 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="R12" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="S12" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
@@ -2655,7 +2652,7 @@
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="183">
   <si>
     <t>#</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>180,288,432</t>
+  </si>
+  <si>
+    <t>80,80,80</t>
   </si>
   <si>
     <t>0.6,0.8,1</t>
@@ -1541,7 +1544,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2039,19 +2042,19 @@
         <v>98</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>86</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S6" s="2" t="s">
         <v>83</v>
@@ -2060,13 +2063,13 @@
         <v>3</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="X6" s="1">
         <v>0</v>
@@ -2075,24 +2078,24 @@
         <v>0</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AC6" s="2"/>
       <c r="AD6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE6" s="1">
         <v>2</v>
       </c>
       <c r="AF6" s="1"/>
       <c r="AG6" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:33">
@@ -2102,7 +2105,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2111,25 +2114,25 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>79</v>
@@ -2138,28 +2141,28 @@
         <v>86</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="T7" s="1">
         <v>3.5</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -2168,24 +2171,24 @@
         <v>0</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AE7" s="1">
         <v>1</v>
       </c>
       <c r="AF7" s="1"/>
       <c r="AG7" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:33">
@@ -2195,7 +2198,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2204,25 +2207,25 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>79</v>
@@ -2231,28 +2234,28 @@
         <v>86</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T8" s="1">
         <v>3.5</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
@@ -2261,24 +2264,24 @@
         <v>0</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AE8" s="1">
         <v>2</v>
       </c>
       <c r="AF8" s="1"/>
       <c r="AG8" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:33">
@@ -2288,7 +2291,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2297,52 +2300,52 @@
         <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T9" s="1">
         <v>2</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W9" s="2" t="s">
         <v>86</v>
@@ -2354,26 +2357,26 @@
         <v>0</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AE9" s="1">
         <v>1</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:33">
@@ -2383,7 +2386,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2392,19 +2395,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>86</v>
@@ -2452,7 +2455,7 @@
         <v>86</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>86</v>
@@ -2466,7 +2469,7 @@
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:33">
@@ -2476,7 +2479,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2485,25 +2488,25 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>86</v>
@@ -2512,10 +2515,10 @@
         <v>86</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>86</v>
@@ -2530,7 +2533,7 @@
         <v>86</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W11" s="2" t="s">
         <v>86</v>
@@ -2559,7 +2562,7 @@
       </c>
       <c r="AF11" s="1"/>
       <c r="AG11" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:33">
@@ -2569,7 +2572,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2578,22 +2581,22 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>86</v>
@@ -2602,28 +2605,28 @@
         <v>86</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>86</v>
@@ -2652,7 +2655,7 @@
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="193">
   <si>
     <t>#</t>
   </si>
@@ -62,6 +62,9 @@
     <t>HeadImgId</t>
   </si>
   <si>
+    <t>ChessPosterId</t>
+  </si>
+  <si>
     <t>MaxHp</t>
   </si>
   <si>
@@ -176,6 +179,9 @@
     <t>棋子头像资源ID（阶级数组，暂时三阶相同）</t>
   </si>
   <si>
+    <t>棋子海报资源Id</t>
+  </si>
+  <si>
     <t>最大生命值（三个阶级）**基础属性**</t>
   </si>
   <si>
@@ -260,6 +266,9 @@
     <t>13001,13001,13001</t>
   </si>
   <si>
+    <t>1511</t>
+  </si>
+  <si>
     <t>520,832,1248</t>
   </si>
   <si>
@@ -320,6 +329,9 @@
     <t>13004,13004,13004</t>
   </si>
   <si>
+    <t>1512</t>
+  </si>
+  <si>
     <t>400,640,960</t>
   </si>
   <si>
@@ -380,6 +392,9 @@
     <t>13010,13010,13010</t>
   </si>
   <si>
+    <t>1513</t>
+  </si>
+  <si>
     <t>600,957,1435</t>
   </si>
   <si>
@@ -434,6 +449,9 @@
     <t>13011,13011,13011</t>
   </si>
   <si>
+    <t>1514</t>
+  </si>
+  <si>
     <t>240,384,576</t>
   </si>
   <si>
@@ -467,9 +485,15 @@
     <t>2312,2312,2312</t>
   </si>
   <si>
+    <t>1312,1312,1312</t>
+  </si>
+  <si>
     <t>13012,13012,13012</t>
   </si>
   <si>
+    <t>1515</t>
+  </si>
+  <si>
     <t>1008,1613,2419</t>
   </si>
   <si>
@@ -506,6 +530,9 @@
     <t>53,53,53</t>
   </si>
   <si>
+    <t>54,54,54</t>
+  </si>
+  <si>
     <t>55,55,55</t>
   </si>
   <si>
@@ -522,6 +549,9 @@
   </si>
   <si>
     <t>2313,2313,2313</t>
+  </si>
+  <si>
+    <t>1313,1313,1313</t>
   </si>
   <si>
     <t>13013,13013,13013</t>
@@ -1543,8 +1573,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AH12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1555,26 +1585,26 @@
     <col min="7" max="8" width="37" customWidth="1"/>
     <col min="9" max="9" width="44" customWidth="1"/>
     <col min="10" max="11" width="42" customWidth="1"/>
-    <col min="12" max="13" width="36" customWidth="1"/>
-    <col min="14" max="14" width="24" customWidth="1"/>
-    <col min="15" max="15" width="32" customWidth="1"/>
-    <col min="16" max="17" width="22" customWidth="1"/>
-    <col min="18" max="19" width="30" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="20" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
-    <col min="23" max="23" width="34" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
-    <col min="26" max="27" width="36" customWidth="1"/>
-    <col min="28" max="28" width="30" customWidth="1"/>
-    <col min="29" max="29" width="44" customWidth="1"/>
-    <col min="30" max="30" width="28" customWidth="1"/>
-    <col min="31" max="31" width="41" customWidth="1"/>
-    <col min="32" max="33" width="50" customWidth="1"/>
+    <col min="12" max="14" width="36" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="32" customWidth="1"/>
+    <col min="17" max="18" width="22" customWidth="1"/>
+    <col min="19" max="20" width="30" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="34" customWidth="1"/>
+    <col min="25" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="28" width="36" customWidth="1"/>
+    <col min="29" max="29" width="30" customWidth="1"/>
+    <col min="30" max="30" width="44" customWidth="1"/>
+    <col min="31" max="31" width="28" customWidth="1"/>
+    <col min="32" max="32" width="41" customWidth="1"/>
+    <col min="33" max="34" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1598,22 +1628,23 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="1"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
-      <c r="X1" s="1"/>
+      <c r="X1" s="2"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="2"/>
+      <c r="Z1" s="1"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
-      <c r="AE1" s="1"/>
+      <c r="AE1" s="2"/>
       <c r="AF1" s="1"/>
-      <c r="AG1" s="2"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="2"/>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:34">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1669,10 +1700,10 @@
       <c r="S2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="V2" s="2" t="s">
@@ -1681,13 +1712,13 @@
       <c r="W2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AA2" s="2" t="s">
@@ -1702,224 +1733,233 @@
       <c r="AD2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="AF2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="AH2" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" spans="1:33">
+    <row r="3" spans="1:34">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="AF3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AG3" s="2" t="s">
-        <v>38</v>
+      <c r="AG3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:33">
+    <row r="4" spans="1:34">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="T4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="U4" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="V4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X4" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="X4" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="Y4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z4" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="Z4" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="AA4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE4" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="AE4" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="AF4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG4" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="AG4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:33">
+    <row r="5" ht="15" customHeight="1" spans="1:34">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
@@ -1928,91 +1968,94 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="T5" s="1">
+        <v>86</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U5" s="1">
         <v>3</v>
       </c>
-      <c r="U5" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="V5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X5" s="1">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="Y5" s="1">
         <v>0</v>
       </c>
-      <c r="Z5" s="2" t="s">
-        <v>87</v>
+      <c r="Z5" s="1">
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE5" s="1">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF5" s="1">
         <v>2</v>
       </c>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="2" t="s">
-        <v>91</v>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:33">
+    <row r="6" ht="15" customHeight="1" spans="1:34">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -2021,91 +2064,94 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="O6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="T6" s="1">
+      <c r="U6" s="1">
         <v>3</v>
       </c>
-      <c r="U6" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="V6" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="X6" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
       </c>
-      <c r="Z6" s="2" t="s">
-        <v>106</v>
+      <c r="Z6" s="1">
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE6" s="1">
+        <v>111</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF6" s="1">
         <v>2</v>
       </c>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="2" t="s">
-        <v>110</v>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:33">
+    <row r="7" ht="15" customHeight="1" spans="1:34">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>10</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2114,91 +2160,94 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="T7" s="1">
+        <v>126</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="U7" s="1">
         <v>3.5</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="V7" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="X7" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="Y7" s="1">
         <v>0</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>125</v>
+      <c r="Z7" s="1">
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE7" s="1">
+        <v>131</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF7" s="1">
         <v>1</v>
       </c>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="2" t="s">
-        <v>129</v>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:33">
+    <row r="8" ht="15" customHeight="1" spans="1:34">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>11</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2207,91 +2256,94 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="T8" s="1">
+        <v>126</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U8" s="1">
         <v>3.5</v>
       </c>
-      <c r="U8" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="V8" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="X8" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="Y8" s="1">
         <v>0</v>
       </c>
-      <c r="Z8" s="2" t="s">
-        <v>139</v>
+      <c r="Z8" s="1">
+        <v>0</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AE8" s="1">
+        <v>146</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AF8" s="1">
         <v>2</v>
       </c>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="2" t="s">
-        <v>143</v>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:33">
+    <row r="9" ht="15" customHeight="1" spans="1:34">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>12</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2300,93 +2352,98 @@
         <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="T9" s="1">
+        <v>160</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="U9" s="1">
         <v>2</v>
       </c>
-      <c r="U9" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="V9" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X9" s="1">
-        <v>0</v>
+        <v>163</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="Y9" s="1">
         <v>0</v>
       </c>
-      <c r="Z9" s="2" t="s">
-        <v>156</v>
+      <c r="Z9" s="1">
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="AD9" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE9" s="1">
+        <v>167</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="AF9" s="1">
         <v>1</v>
       </c>
-      <c r="AF9" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG9" s="2" t="s">
-        <v>161</v>
+      <c r="AG9" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:33">
+    <row r="10" ht="15" customHeight="1" spans="1:34">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>13</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2395,91 +2452,94 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T10" s="1">
+        <v>89</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U10" s="1">
         <v>4</v>
       </c>
-      <c r="U10" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="V10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X10" s="1">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
       </c>
-      <c r="Z10" s="2" t="s">
-        <v>86</v>
+      <c r="Z10" s="1">
+        <v>0</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE10" s="1">
+        <v>176</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF10" s="1">
         <v>1</v>
       </c>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="2" t="s">
-        <v>167</v>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:33">
+    <row r="11" ht="15" customHeight="1" spans="1:34">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>9999</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2488,91 +2548,94 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>172</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T11" s="1">
+        <v>89</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U11" s="1">
         <v>0</v>
       </c>
-      <c r="U11" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="V11" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X11" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>86</v>
+      <c r="Z11" s="1">
+        <v>0</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE11" s="1">
+        <v>89</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF11" s="1">
         <v>3</v>
       </c>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="2" t="s">
-        <v>175</v>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:33">
+    <row r="12" ht="15" customHeight="1" spans="1:34">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1001</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2581,81 +2644,84 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="T12" s="1">
+        <v>192</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="U12" s="1">
         <v>0</v>
       </c>
-      <c r="U12" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="V12" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="X12" s="1">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
       </c>
-      <c r="Z12" s="2" t="s">
-        <v>86</v>
+      <c r="Z12" s="1">
+        <v>0</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE12" s="1">
+        <v>89</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="2" t="s">
-        <v>175</v>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1574,7 +1574,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="195">
   <si>
     <t>#</t>
   </si>
@@ -479,7 +479,7 @@
     <t>恶魂是世间所有邪恶与负面能量的聚合体，它没有固定的形态，只是一团扭曲的黑暗。它在人性的恐惧和绝望中诞生，随处可见的罪恶为它不断补充力量。,恶魂已经成长为足以威胁一方的存在。它会化作人们心中的梦魇，引发更多的杀戮和痛苦。它的力量来自于每一个选择了黑暗的灵魂。,恶魂已经演化到了巅峰形态，成为了黑暗本身的化身。它不再是单纯的能量集合，而是拥有了自己的意志和野心，渴望吞噬整个世界的光明。</t>
   </si>
   <si>
-    <t>黑暗杨戬</t>
+    <t>黑化杨戬</t>
   </si>
   <si>
     <t>2312,2312,2312</t>
@@ -542,7 +542,7 @@
     <t>杨戬曾是天界的神将，正义与力量的象征。但一次任务中，他被黑暗力量击中，虽然活了下来，但那股邪恶的能量开始侵蚀他的灵魂。他痛苦地与黑暗对抗，但最终还是逐渐沦陷。,黑暗完全控制了杨戬。他失去了自我，成为了黑暗的傀儡。他挥舞着曾经守护天界的神兵，却用来摧毁一切美好。他的力量被黑暗扭曲，变得更加恐怖。,黑暗杨戬已经完全进化，成为了黑暗势力的最强战士。他不再是曾经的神将，而是黑暗的化身。他召唤出了黑暗的仆从——哮天犬，一同在黑暗中肆虐。</t>
   </si>
   <si>
-    <t>黑暗哮天犬</t>
+    <t>哮天犬</t>
   </si>
   <si>
     <t>-1</t>
@@ -561,6 +561,12 @@
   </si>
   <si>
     <t>哮天犬是杨戬最忠诚的伙伴，曾与他一同守护天界。然而，当杨戬被黑暗侵蚀时，哮天犬也未能幸免。它感受到了主人的痛苦和堕落，却无力阻止。,黑暗哮天犬已经完全被邪恶所控制。它失去了原有的忠诚和温顺，化作了黑暗的猎犬。它会毫不犹豫地为主人撕碎任何敌人，无论对手是谁。,黑暗哮天犬已经演化成了黑暗的完美战兽，拥有难以抵挡的力量。它与黑暗杨戬一同出现，为黑暗势力扫平一切障碍。</t>
+  </si>
+  <si>
+    <t>黑化后羿</t>
+  </si>
+  <si>
+    <t>黑化嫦娥</t>
   </si>
   <si>
     <t>稻草人</t>
@@ -1573,7 +1579,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2535,68 +2541,68 @@
     <row r="11" ht="15" customHeight="1" spans="1:34">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
-        <v>9999</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
         <v>178</v>
       </c>
       <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>182</v>
+        <v>80</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>184</v>
+        <v>85</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="U11" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>89</v>
@@ -2608,85 +2614,83 @@
         <v>0</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AD11" s="2"/>
       <c r="AE11" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AF11" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG11" s="1"/>
-      <c r="AH11" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="AH11" s="2"/>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:34">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
-        <v>1001</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E12" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>172</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="U12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="s">
         <v>107</v>
@@ -2695,7 +2699,7 @@
         <v>108</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -2704,24 +2708,214 @@
         <v>0</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="AD12" s="2"/>
       <c r="AE12" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="AF12" s="1">
+        <v>2</v>
+      </c>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="2"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:34">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>9999</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>185</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD13" s="2"/>
+      <c r="AE13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:34">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -2355,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>116</v>

--- a/AAAGameData/DataTables/SummonChessTable.xlsx
+++ b/AAAGameData/DataTables/SummonChessTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1580,7 +1580,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
